--- a/diseases/d155/2000-2004.xlsx
+++ b/diseases/d155/2000-2004.xlsx
@@ -913,9 +913,6 @@
       <c r="O3" t="n">
         <v>40</v>
       </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
       <c r="R3" t="n">
         <v>0.7727674434621603</v>
       </c>
@@ -1309,9 +1306,6 @@
       <c r="O5" t="n">
         <v>14</v>
       </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
       <c r="R5" t="n">
         <v>0.3117438124976759</v>
       </c>
@@ -1853,9 +1847,6 @@
       <c r="O8" t="n">
         <v>43</v>
       </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
       <c r="R8" t="n">
         <v>0.8307250017218224</v>
       </c>
@@ -2249,9 +2240,6 @@
       <c r="O10" t="n">
         <v>5</v>
       </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
       <c r="R10" t="n">
         <v>0.1113370758920271</v>
       </c>
@@ -2793,9 +2781,6 @@
       <c r="O13" t="n">
         <v>52</v>
       </c>
-      <c r="Q13" t="n">
-        <v>0</v>
-      </c>
       <c r="R13" t="n">
         <v>1.004597676500808</v>
       </c>
@@ -3189,9 +3174,6 @@
       <c r="O15" t="n">
         <v>6</v>
       </c>
-      <c r="Q15" t="n">
-        <v>0</v>
-      </c>
       <c r="R15" t="n">
         <v>0.1336044910704325</v>
       </c>
@@ -3733,9 +3715,6 @@
       <c r="O18" t="n">
         <v>52</v>
       </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
       <c r="R18" t="n">
         <v>1.004597676500808</v>
       </c>
@@ -4129,9 +4108,6 @@
       <c r="O20" t="n">
         <v>8</v>
       </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
       <c r="R20" t="n">
         <v>0.1781393214272433</v>
       </c>
@@ -4673,9 +4649,6 @@
       <c r="O23" t="n">
         <v>79</v>
       </c>
-      <c r="Q23" t="n">
-        <v>0</v>
-      </c>
       <c r="R23" t="n">
         <v>1.526215700837767</v>
       </c>
@@ -5069,9 +5042,6 @@
       <c r="O25" t="n">
         <v>7</v>
       </c>
-      <c r="Q25" t="n">
-        <v>0</v>
-      </c>
       <c r="R25" t="n">
         <v>0.1558719062488379</v>
       </c>
@@ -5613,9 +5583,6 @@
       <c r="O28" t="n">
         <v>70</v>
       </c>
-      <c r="Q28" t="n">
-        <v>0</v>
-      </c>
       <c r="R28" t="n">
         <v>1.352343026058781</v>
       </c>
@@ -6009,9 +5976,6 @@
       <c r="O30" t="n">
         <v>14</v>
       </c>
-      <c r="Q30" t="n">
-        <v>0</v>
-      </c>
       <c r="R30" t="n">
         <v>0.3117438124976759</v>
       </c>
@@ -6553,9 +6517,6 @@
       <c r="O33" t="n">
         <v>63</v>
       </c>
-      <c r="Q33" t="n">
-        <v>0</v>
-      </c>
       <c r="R33" t="n">
         <v>1.217108723452903</v>
       </c>
@@ -6949,9 +6910,6 @@
       <c r="O35" t="n">
         <v>12</v>
       </c>
-      <c r="Q35" t="n">
-        <v>0</v>
-      </c>
       <c r="R35" t="n">
         <v>0.267208982140865</v>
       </c>
@@ -7493,9 +7451,6 @@
       <c r="O38" t="n">
         <v>60</v>
       </c>
-      <c r="Q38" t="n">
-        <v>0</v>
-      </c>
       <c r="R38" t="n">
         <v>1.159151165193241</v>
       </c>
@@ -7889,9 +7844,6 @@
       <c r="O40" t="n">
         <v>16</v>
       </c>
-      <c r="Q40" t="n">
-        <v>0</v>
-      </c>
       <c r="R40" t="n">
         <v>0.3562786428544867</v>
       </c>
@@ -8433,9 +8385,6 @@
       <c r="O43" t="n">
         <v>43</v>
       </c>
-      <c r="Q43" t="n">
-        <v>0</v>
-      </c>
       <c r="R43" t="n">
         <v>0.8307250017218224</v>
       </c>
@@ -8829,9 +8778,6 @@
       <c r="O45" t="n">
         <v>22</v>
       </c>
-      <c r="Q45" t="n">
-        <v>0</v>
-      </c>
       <c r="R45" t="n">
         <v>0.4898831339249192</v>
       </c>
@@ -9373,9 +9319,6 @@
       <c r="O48" t="n">
         <v>51</v>
       </c>
-      <c r="Q48" t="n">
-        <v>0</v>
-      </c>
       <c r="R48" t="n">
         <v>0.9852784904142545</v>
       </c>
@@ -9769,9 +9712,6 @@
       <c r="O50" t="n">
         <v>9</v>
       </c>
-      <c r="Q50" t="n">
-        <v>0</v>
-      </c>
       <c r="R50" t="n">
         <v>0.2004067366056487</v>
       </c>
@@ -10313,9 +10253,6 @@
       <c r="O53" t="n">
         <v>49</v>
       </c>
-      <c r="Q53" t="n">
-        <v>0</v>
-      </c>
       <c r="R53" t="n">
         <v>0.9466401182411465</v>
       </c>
@@ -10709,9 +10646,6 @@
       <c r="O55" t="n">
         <v>12</v>
       </c>
-      <c r="Q55" t="n">
-        <v>0</v>
-      </c>
       <c r="R55" t="n">
         <v>0.267208982140865</v>
       </c>
@@ -11253,9 +11187,6 @@
       <c r="O58" t="n">
         <v>40</v>
       </c>
-      <c r="Q58" t="n">
-        <v>0</v>
-      </c>
       <c r="R58" t="n">
         <v>0.7727674434621603</v>
       </c>
@@ -11649,9 +11580,6 @@
       <c r="O60" t="n">
         <v>8</v>
       </c>
-      <c r="Q60" t="n">
-        <v>0</v>
-      </c>
       <c r="R60" t="n">
         <v>0.1781393214272433</v>
       </c>
@@ -12193,9 +12121,6 @@
       <c r="O63" t="n">
         <v>58</v>
       </c>
-      <c r="Q63" t="n">
-        <v>0</v>
-      </c>
       <c r="R63" t="n">
         <v>1.11797078279736</v>
       </c>
@@ -12589,9 +12514,6 @@
       <c r="O65" t="n">
         <v>14</v>
       </c>
-      <c r="Q65" t="n">
-        <v>0</v>
-      </c>
       <c r="R65" t="n">
         <v>0.3101697802912362</v>
       </c>
@@ -13133,9 +13055,6 @@
       <c r="O68" t="n">
         <v>31</v>
       </c>
-      <c r="Q68" t="n">
-        <v>0</v>
-      </c>
       <c r="R68" t="n">
         <v>0.5975361080468645</v>
       </c>
@@ -13529,9 +13448,6 @@
       <c r="O70" t="n">
         <v>2</v>
       </c>
-      <c r="Q70" t="n">
-        <v>0</v>
-      </c>
       <c r="R70" t="n">
         <v>0.04430996861303373</v>
       </c>
@@ -14073,9 +13989,6 @@
       <c r="O73" t="n">
         <v>55</v>
       </c>
-      <c r="Q73" t="n">
-        <v>0</v>
-      </c>
       <c r="R73" t="n">
         <v>1.060144707825082</v>
       </c>
@@ -14469,9 +14382,6 @@
       <c r="O75" t="n">
         <v>7</v>
       </c>
-      <c r="Q75" t="n">
-        <v>0</v>
-      </c>
       <c r="R75" t="n">
         <v>0.1550848901456181</v>
       </c>
@@ -15013,9 +14923,6 @@
       <c r="O78" t="n">
         <v>69</v>
       </c>
-      <c r="Q78" t="n">
-        <v>0</v>
-      </c>
       <c r="R78" t="n">
         <v>1.329999724362376</v>
       </c>
@@ -15409,9 +15316,6 @@
       <c r="O80" t="n">
         <v>2</v>
       </c>
-      <c r="Q80" t="n">
-        <v>0</v>
-      </c>
       <c r="R80" t="n">
         <v>0.04430996861303373</v>
       </c>
@@ -15953,9 +15857,6 @@
       <c r="O83" t="n">
         <v>88</v>
       </c>
-      <c r="Q83" t="n">
-        <v>0</v>
-      </c>
       <c r="R83" t="n">
         <v>1.696231532520132</v>
       </c>
@@ -16349,9 +16250,6 @@
       <c r="O85" t="n">
         <v>4</v>
       </c>
-      <c r="Q85" t="n">
-        <v>0</v>
-      </c>
       <c r="R85" t="n">
         <v>0.08861993722606747</v>
       </c>
@@ -16893,9 +16791,6 @@
       <c r="O88" t="n">
         <v>110</v>
       </c>
-      <c r="Q88" t="n">
-        <v>0</v>
-      </c>
       <c r="R88" t="n">
         <v>2.120289415650165</v>
       </c>
@@ -17289,9 +17184,6 @@
       <c r="O90" t="n">
         <v>6</v>
       </c>
-      <c r="Q90" t="n">
-        <v>0</v>
-      </c>
       <c r="R90" t="n">
         <v>0.1329299058391012</v>
       </c>
@@ -17833,9 +17725,6 @@
       <c r="O93" t="n">
         <v>82</v>
       </c>
-      <c r="Q93" t="n">
-        <v>0</v>
-      </c>
       <c r="R93" t="n">
         <v>1.580579382575577</v>
       </c>
@@ -18229,9 +18118,6 @@
       <c r="O95" t="n">
         <v>12</v>
       </c>
-      <c r="Q95" t="n">
-        <v>0</v>
-      </c>
       <c r="R95" t="n">
         <v>0.2658598116782024</v>
       </c>
@@ -18773,9 +18659,6 @@
       <c r="O98" t="n">
         <v>65</v>
       </c>
-      <c r="Q98" t="n">
-        <v>0</v>
-      </c>
       <c r="R98" t="n">
         <v>1.252898291066006</v>
       </c>
@@ -19169,9 +19052,6 @@
       <c r="O100" t="n">
         <v>16</v>
       </c>
-      <c r="Q100" t="n">
-        <v>0</v>
-      </c>
       <c r="R100" t="n">
         <v>0.3544797489042699</v>
       </c>
@@ -19713,9 +19593,6 @@
       <c r="O103" t="n">
         <v>50</v>
       </c>
-      <c r="Q103" t="n">
-        <v>0</v>
-      </c>
       <c r="R103" t="n">
         <v>0.9637679162046202</v>
       </c>
@@ -20109,9 +19986,6 @@
       <c r="O105" t="n">
         <v>16</v>
       </c>
-      <c r="Q105" t="n">
-        <v>0</v>
-      </c>
       <c r="R105" t="n">
         <v>0.3544797489042699</v>
       </c>
@@ -20653,9 +20527,6 @@
       <c r="O108" t="n">
         <v>54</v>
       </c>
-      <c r="Q108" t="n">
-        <v>0</v>
-      </c>
       <c r="R108" t="n">
         <v>1.04086934950099</v>
       </c>
@@ -21049,9 +20920,6 @@
       <c r="O110" t="n">
         <v>12</v>
       </c>
-      <c r="Q110" t="n">
-        <v>0</v>
-      </c>
       <c r="R110" t="n">
         <v>0.2658598116782024</v>
       </c>
@@ -21593,9 +21461,6 @@
       <c r="O113" t="n">
         <v>35</v>
       </c>
-      <c r="Q113" t="n">
-        <v>0</v>
-      </c>
       <c r="R113" t="n">
         <v>0.6746375413432342</v>
       </c>
@@ -21989,9 +21854,6 @@
       <c r="O115" t="n">
         <v>14</v>
       </c>
-      <c r="Q115" t="n">
-        <v>0</v>
-      </c>
       <c r="R115" t="n">
         <v>0.3101697802912362</v>
       </c>
@@ -22533,9 +22395,6 @@
       <c r="O118" t="n">
         <v>35</v>
       </c>
-      <c r="Q118" t="n">
-        <v>0</v>
-      </c>
       <c r="R118" t="n">
         <v>0.6746375413432342</v>
       </c>
@@ -22929,9 +22788,6 @@
       <c r="O120" t="n">
         <v>9</v>
       </c>
-      <c r="Q120" t="n">
-        <v>0</v>
-      </c>
       <c r="R120" t="n">
         <v>0.1993948587586518</v>
       </c>
@@ -23473,9 +23329,6 @@
       <c r="O123" t="n">
         <v>52</v>
       </c>
-      <c r="Q123" t="n">
-        <v>0</v>
-      </c>
       <c r="R123" t="n">
         <v>0.9998950110238425</v>
       </c>
@@ -23869,9 +23722,6 @@
       <c r="O125" t="n">
         <v>6</v>
       </c>
-      <c r="Q125" t="n">
-        <v>0</v>
-      </c>
       <c r="R125" t="n">
         <v>0.132216427714855</v>
       </c>
@@ -24413,9 +24263,6 @@
       <c r="O128" t="n">
         <v>45</v>
       </c>
-      <c r="Q128" t="n">
-        <v>0</v>
-      </c>
       <c r="R128" t="n">
         <v>0.8652937595398636</v>
       </c>
@@ -24809,9 +24656,6 @@
       <c r="O130" t="n">
         <v>4</v>
       </c>
-      <c r="Q130" t="n">
-        <v>0</v>
-      </c>
       <c r="R130" t="n">
         <v>0.08814428514323666</v>
       </c>
@@ -25353,9 +25197,6 @@
       <c r="O133" t="n">
         <v>55</v>
       </c>
-      <c r="Q133" t="n">
-        <v>0</v>
-      </c>
       <c r="R133" t="n">
         <v>1.057581261659833</v>
       </c>
@@ -25749,9 +25590,6 @@
       <c r="O135" t="n">
         <v>2</v>
       </c>
-      <c r="Q135" t="n">
-        <v>0</v>
-      </c>
       <c r="R135" t="n">
         <v>0.04407214257161833</v>
       </c>
@@ -26293,9 +26131,6 @@
       <c r="O138" t="n">
         <v>72</v>
       </c>
-      <c r="Q138" t="n">
-        <v>0</v>
-      </c>
       <c r="R138" t="n">
         <v>1.384470015263782</v>
       </c>
@@ -26689,9 +26524,6 @@
       <c r="O140" t="n">
         <v>6</v>
       </c>
-      <c r="Q140" t="n">
-        <v>0</v>
-      </c>
       <c r="R140" t="n">
         <v>0.132216427714855</v>
       </c>
@@ -27233,9 +27065,6 @@
       <c r="O143" t="n">
         <v>78</v>
       </c>
-      <c r="Q143" t="n">
-        <v>0</v>
-      </c>
       <c r="R143" t="n">
         <v>1.499842516535764</v>
       </c>
@@ -27629,9 +27458,6 @@
       <c r="O145" t="n">
         <v>12</v>
       </c>
-      <c r="Q145" t="n">
-        <v>0</v>
-      </c>
       <c r="R145" t="n">
         <v>0.26443285542971</v>
       </c>
@@ -28173,9 +27999,6 @@
       <c r="O148" t="n">
         <v>65</v>
       </c>
-      <c r="Q148" t="n">
-        <v>0</v>
-      </c>
       <c r="R148" t="n">
         <v>1.249868763779803</v>
       </c>
@@ -28569,9 +28392,6 @@
       <c r="O150" t="n">
         <v>10</v>
       </c>
-      <c r="Q150" t="n">
-        <v>0</v>
-      </c>
       <c r="R150" t="n">
         <v>0.2203607128580917</v>
       </c>
@@ -29113,9 +28933,6 @@
       <c r="O153" t="n">
         <v>56</v>
       </c>
-      <c r="Q153" t="n">
-        <v>0</v>
-      </c>
       <c r="R153" t="n">
         <v>1.07681001187183</v>
       </c>
@@ -29509,9 +29326,6 @@
       <c r="O155" t="n">
         <v>10</v>
       </c>
-      <c r="Q155" t="n">
-        <v>0</v>
-      </c>
       <c r="R155" t="n">
         <v>0.2203607128580917</v>
       </c>
@@ -30053,9 +29867,6 @@
       <c r="O158" t="n">
         <v>100</v>
       </c>
-      <c r="Q158" t="n">
-        <v>0</v>
-      </c>
       <c r="R158" t="n">
         <v>1.922875021199697</v>
       </c>
@@ -30449,9 +30260,6 @@
       <c r="O160" t="n">
         <v>17</v>
       </c>
-      <c r="Q160" t="n">
-        <v>0</v>
-      </c>
       <c r="R160" t="n">
         <v>0.3746132118587558</v>
       </c>
@@ -30993,9 +30801,6 @@
       <c r="O163" t="n">
         <v>53</v>
       </c>
-      <c r="Q163" t="n">
-        <v>0</v>
-      </c>
       <c r="R163" t="n">
         <v>1.019123761235839</v>
       </c>
@@ -31389,9 +31194,6 @@
       <c r="O165" t="n">
         <v>13</v>
       </c>
-      <c r="Q165" t="n">
-        <v>0</v>
-      </c>
       <c r="R165" t="n">
         <v>0.2864689267155192</v>
       </c>
@@ -31933,9 +31735,6 @@
       <c r="O168" t="n">
         <v>40</v>
       </c>
-      <c r="Q168" t="n">
-        <v>0</v>
-      </c>
       <c r="R168" t="n">
         <v>0.7691500084798788</v>
       </c>
@@ -32329,9 +32128,6 @@
       <c r="O170" t="n">
         <v>9</v>
       </c>
-      <c r="Q170" t="n">
-        <v>0</v>
-      </c>
       <c r="R170" t="n">
         <v>0.1983246415722825</v>
       </c>
@@ -32873,9 +32669,6 @@
       <c r="O173" t="n">
         <v>50</v>
       </c>
-      <c r="Q173" t="n">
-        <v>0</v>
-      </c>
       <c r="R173" t="n">
         <v>0.9614375105998486</v>
       </c>
@@ -33269,9 +33062,6 @@
       <c r="O175" t="n">
         <v>6</v>
       </c>
-      <c r="Q175" t="n">
-        <v>0</v>
-      </c>
       <c r="R175" t="n">
         <v>0.132216427714855</v>
       </c>
@@ -33813,9 +33603,6 @@
       <c r="O178" t="n">
         <v>30</v>
       </c>
-      <c r="Q178" t="n">
-        <v>0</v>
-      </c>
       <c r="R178" t="n">
         <v>0.5768625063599091</v>
       </c>
@@ -34209,9 +33996,6 @@
       <c r="O180" t="n">
         <v>5</v>
       </c>
-      <c r="Q180" t="n">
-        <v>0</v>
-      </c>
       <c r="R180" t="n">
         <v>0.1101803564290458</v>
       </c>
@@ -34753,9 +34537,6 @@
       <c r="O183" t="n">
         <v>35</v>
       </c>
-      <c r="Q183" t="n">
-        <v>0</v>
-      </c>
       <c r="R183" t="n">
         <v>0.6714042227489015</v>
       </c>
@@ -35149,9 +34930,6 @@
       <c r="O185" t="n">
         <v>9</v>
       </c>
-      <c r="Q185" t="n">
-        <v>0</v>
-      </c>
       <c r="R185" t="n">
         <v>0.1971665415389375</v>
       </c>
@@ -35693,9 +35471,6 @@
       <c r="O188" t="n">
         <v>42</v>
       </c>
-      <c r="Q188" t="n">
-        <v>0</v>
-      </c>
       <c r="R188" t="n">
         <v>0.8056850672986818</v>
       </c>
@@ -36089,9 +35864,6 @@
       <c r="O190" t="n">
         <v>6</v>
       </c>
-      <c r="Q190" t="n">
-        <v>0</v>
-      </c>
       <c r="R190" t="n">
         <v>0.1314443610259583</v>
       </c>
@@ -36633,9 +36405,6 @@
       <c r="O193" t="n">
         <v>58</v>
       </c>
-      <c r="Q193" t="n">
-        <v>0</v>
-      </c>
       <c r="R193" t="n">
         <v>1.112612711983894</v>
       </c>
@@ -37029,9 +36798,6 @@
       <c r="O195" t="n">
         <v>7</v>
       </c>
-      <c r="Q195" t="n">
-        <v>0</v>
-      </c>
       <c r="R195" t="n">
         <v>0.1533517545302847</v>
       </c>
@@ -37573,9 +37339,6 @@
       <c r="O198" t="n">
         <v>39</v>
       </c>
-      <c r="Q198" t="n">
-        <v>0</v>
-      </c>
       <c r="R198" t="n">
         <v>0.7481361339202046</v>
       </c>
@@ -37969,9 +37732,6 @@
       <c r="O200" t="n">
         <v>5</v>
       </c>
-      <c r="Q200" t="n">
-        <v>0</v>
-      </c>
       <c r="R200" t="n">
         <v>0.1095369675216319</v>
       </c>
@@ -38513,9 +38273,6 @@
       <c r="O203" t="n">
         <v>128</v>
       </c>
-      <c r="Q203" t="n">
-        <v>0</v>
-      </c>
       <c r="R203" t="n">
         <v>2.455421157481697</v>
       </c>
@@ -38909,9 +38666,6 @@
       <c r="O205" t="n">
         <v>2</v>
       </c>
-      <c r="Q205" t="n">
-        <v>0</v>
-      </c>
       <c r="R205" t="n">
         <v>0.04381478700865277</v>
       </c>
@@ -39453,9 +39207,6 @@
       <c r="O208" t="n">
         <v>114</v>
       </c>
-      <c r="Q208" t="n">
-        <v>0</v>
-      </c>
       <c r="R208" t="n">
         <v>2.186859468382136</v>
       </c>
@@ -39849,9 +39600,6 @@
       <c r="O210" t="n">
         <v>4</v>
       </c>
-      <c r="Q210" t="n">
-        <v>0</v>
-      </c>
       <c r="R210" t="n">
         <v>0.08762957401730553</v>
       </c>
@@ -40393,9 +40141,6 @@
       <c r="O213" t="n">
         <v>43</v>
       </c>
-      <c r="Q213" t="n">
-        <v>0</v>
-      </c>
       <c r="R213" t="n">
         <v>0.8248680450915076</v>
       </c>
@@ -40789,9 +40534,6 @@
       <c r="O215" t="n">
         <v>13</v>
       </c>
-      <c r="Q215" t="n">
-        <v>0</v>
-      </c>
       <c r="R215" t="n">
         <v>0.284796115556243</v>
       </c>
@@ -41333,9 +41075,6 @@
       <c r="O218" t="n">
         <v>53</v>
       </c>
-      <c r="Q218" t="n">
-        <v>0</v>
-      </c>
       <c r="R218" t="n">
         <v>1.016697823019765</v>
       </c>
@@ -41729,9 +41468,6 @@
       <c r="O220" t="n">
         <v>7</v>
       </c>
-      <c r="Q220" t="n">
-        <v>0</v>
-      </c>
       <c r="R220" t="n">
         <v>0.1533517545302847</v>
       </c>
@@ -42273,9 +42009,6 @@
       <c r="O223" t="n">
         <v>23</v>
       </c>
-      <c r="Q223" t="n">
-        <v>0</v>
-      </c>
       <c r="R223" t="n">
         <v>0.4412084892349924</v>
       </c>
@@ -42669,9 +42402,6 @@
       <c r="O225" t="n">
         <v>9</v>
       </c>
-      <c r="Q225" t="n">
-        <v>0</v>
-      </c>
       <c r="R225" t="n">
         <v>0.1971665415389375</v>
       </c>
@@ -43213,9 +42943,6 @@
       <c r="O228" t="n">
         <v>34</v>
       </c>
-      <c r="Q228" t="n">
-        <v>0</v>
-      </c>
       <c r="R228" t="n">
         <v>0.6522212449560758</v>
       </c>
@@ -43609,9 +43336,6 @@
       <c r="O230" t="n">
         <v>11</v>
       </c>
-      <c r="Q230" t="n">
-        <v>0</v>
-      </c>
       <c r="R230" t="n">
         <v>0.2409813285475902</v>
       </c>
@@ -44153,9 +43877,6 @@
       <c r="O233" t="n">
         <v>44</v>
       </c>
-      <c r="Q233" t="n">
-        <v>0</v>
-      </c>
       <c r="R233" t="n">
         <v>0.8440510228843334</v>
       </c>
@@ -44549,9 +44270,6 @@
       <c r="O235" t="n">
         <v>5</v>
       </c>
-      <c r="Q235" t="n">
-        <v>0</v>
-      </c>
       <c r="R235" t="n">
         <v>0.1095369675216319</v>
       </c>
@@ -45093,9 +44811,6 @@
       <c r="O238" t="n">
         <v>47</v>
       </c>
-      <c r="Q238" t="n">
-        <v>0</v>
-      </c>
       <c r="R238" t="n">
         <v>0.9015999562628106</v>
       </c>
@@ -45489,9 +45204,6 @@
       <c r="O240" t="n">
         <v>2</v>
       </c>
-      <c r="Q240" t="n">
-        <v>0</v>
-      </c>
       <c r="R240" t="n">
         <v>0.04381478700865277</v>
       </c>
@@ -46033,9 +45745,6 @@
       <c r="O243" t="n">
         <v>53</v>
       </c>
-      <c r="Q243" t="n">
-        <v>0</v>
-      </c>
       <c r="R243" t="n">
         <v>1.013743298774251</v>
       </c>
@@ -46429,9 +46138,6 @@
       <c r="O245" t="n">
         <v>7</v>
       </c>
-      <c r="Q245" t="n">
-        <v>0</v>
-      </c>
       <c r="R245" t="n">
         <v>0.152447573007415</v>
       </c>
@@ -46973,9 +46679,6 @@
       <c r="O248" t="n">
         <v>46</v>
       </c>
-      <c r="Q248" t="n">
-        <v>0</v>
-      </c>
       <c r="R248" t="n">
         <v>0.87985267440784</v>
       </c>
@@ -47369,9 +47072,6 @@
       <c r="O250" t="n">
         <v>7</v>
       </c>
-      <c r="Q250" t="n">
-        <v>0</v>
-      </c>
       <c r="R250" t="n">
         <v>0.152447573007415</v>
       </c>
@@ -47913,9 +47613,6 @@
       <c r="O253" t="n">
         <v>83</v>
       </c>
-      <c r="Q253" t="n">
-        <v>0</v>
-      </c>
       <c r="R253" t="n">
         <v>1.587560260344581</v>
       </c>
@@ -48309,9 +48006,6 @@
       <c r="O255" t="n">
         <v>4</v>
       </c>
-      <c r="Q255" t="n">
-        <v>0</v>
-      </c>
       <c r="R255" t="n">
         <v>0.08711289886137998</v>
       </c>
@@ -48853,9 +48547,6 @@
       <c r="O258" t="n">
         <v>70</v>
       </c>
-      <c r="Q258" t="n">
-        <v>0</v>
-      </c>
       <c r="R258" t="n">
         <v>1.338906243664104</v>
       </c>
@@ -49249,9 +48940,6 @@
       <c r="O260" t="n">
         <v>6</v>
       </c>
-      <c r="Q260" t="n">
-        <v>0</v>
-      </c>
       <c r="R260" t="n">
         <v>0.1306693482920699</v>
       </c>
@@ -49793,9 +49481,6 @@
       <c r="O263" t="n">
         <v>63</v>
       </c>
-      <c r="Q263" t="n">
-        <v>0</v>
-      </c>
       <c r="R263" t="n">
         <v>1.205015619297694</v>
       </c>
@@ -50189,9 +49874,6 @@
       <c r="O265" t="n">
         <v>5</v>
       </c>
-      <c r="Q265" t="n">
-        <v>0</v>
-      </c>
       <c r="R265" t="n">
         <v>0.108891123576725</v>
       </c>
@@ -50733,9 +50415,6 @@
       <c r="O268" t="n">
         <v>86</v>
       </c>
-      <c r="Q268" t="n">
-        <v>0</v>
-      </c>
       <c r="R268" t="n">
         <v>1.644941956501614</v>
       </c>
@@ -51129,9 +50808,6 @@
       <c r="O270" t="n">
         <v>7</v>
       </c>
-      <c r="Q270" t="n">
-        <v>0</v>
-      </c>
       <c r="R270" t="n">
         <v>0.152447573007415</v>
       </c>
@@ -51673,9 +51349,6 @@
       <c r="O273" t="n">
         <v>62</v>
       </c>
-      <c r="Q273" t="n">
-        <v>0</v>
-      </c>
       <c r="R273" t="n">
         <v>1.18588838724535</v>
       </c>
@@ -52069,9 +51742,6 @@
       <c r="O275" t="n">
         <v>7</v>
       </c>
-      <c r="Q275" t="n">
-        <v>0</v>
-      </c>
       <c r="R275" t="n">
         <v>0.152447573007415</v>
       </c>
@@ -52613,9 +52283,6 @@
       <c r="O278" t="n">
         <v>46</v>
       </c>
-      <c r="Q278" t="n">
-        <v>0</v>
-      </c>
       <c r="R278" t="n">
         <v>0.87985267440784</v>
       </c>
@@ -53009,9 +52676,6 @@
       <c r="O280" t="n">
         <v>13</v>
       </c>
-      <c r="Q280" t="n">
-        <v>0</v>
-      </c>
       <c r="R280" t="n">
         <v>0.2831169212994849</v>
       </c>
@@ -53553,9 +53217,6 @@
       <c r="O283" t="n">
         <v>35</v>
       </c>
-      <c r="Q283" t="n">
-        <v>0</v>
-      </c>
       <c r="R283" t="n">
         <v>0.6694531218320522</v>
       </c>
@@ -53949,9 +53610,6 @@
       <c r="O285" t="n">
         <v>10</v>
       </c>
-      <c r="Q285" t="n">
-        <v>0</v>
-      </c>
       <c r="R285" t="n">
         <v>0.2177822471534499</v>
       </c>
@@ -54493,9 +54151,6 @@
       <c r="O288" t="n">
         <v>50</v>
       </c>
-      <c r="Q288" t="n">
-        <v>0</v>
-      </c>
       <c r="R288" t="n">
         <v>0.9563616026172175</v>
       </c>
@@ -54889,9 +54544,6 @@
       <c r="O290" t="n">
         <v>8</v>
       </c>
-      <c r="Q290" t="n">
-        <v>0</v>
-      </c>
       <c r="R290" t="n">
         <v>0.17422579772276</v>
       </c>
@@ -55433,9 +55085,6 @@
       <c r="O293" t="n">
         <v>46</v>
       </c>
-      <c r="Q293" t="n">
-        <v>0</v>
-      </c>
       <c r="R293" t="n">
         <v>0.87985267440784</v>
       </c>
@@ -55829,9 +55478,6 @@
       <c r="O295" t="n">
         <v>9</v>
       </c>
-      <c r="Q295" t="n">
-        <v>0</v>
-      </c>
       <c r="R295" t="n">
         <v>0.1960040224381049</v>
       </c>
@@ -56373,9 +56019,6 @@
       <c r="O298" t="n">
         <v>46</v>
       </c>
-      <c r="Q298" t="n">
-        <v>0</v>
-      </c>
       <c r="R298" t="n">
         <v>0.87985267440784</v>
       </c>
@@ -56768,9 +56411,6 @@
       </c>
       <c r="O300" t="n">
         <v>14</v>
-      </c>
-      <c r="Q300" t="n">
-        <v>0</v>
       </c>
       <c r="R300" t="n">
         <v>0.3048951460148299</v>

--- a/diseases/d155/2000-2004.xlsx
+++ b/diseases/d155/2000-2004.xlsx
@@ -938,7 +938,7 @@
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
@@ -946,17 +946,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS3" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1220</t>
         </is>
       </c>
       <c r="AT3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV3" t="inlineStr">
@@ -1172,7 +1177,7 @@
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
@@ -1180,17 +1185,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS4" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1220</t>
         </is>
       </c>
       <c r="AT4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
@@ -1331,7 +1341,7 @@
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
@@ -1339,17 +1349,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR5" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS5" t="inlineStr">
         <is>
           <t>SER_NO_FHI_303_MONTHLY</t>
         </is>
       </c>
       <c r="AT5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
@@ -1565,7 +1580,7 @@
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
@@ -1573,17 +1588,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS6" t="inlineStr">
         <is>
           <t>SER_NO_FHI_303_MONTHLY</t>
         </is>
       </c>
       <c r="AT6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
@@ -1872,7 +1892,7 @@
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
@@ -1880,17 +1900,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR8" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS8" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1220</t>
         </is>
       </c>
       <c r="AT8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
@@ -2106,7 +2131,7 @@
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
@@ -2114,17 +2139,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR9" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS9" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1220</t>
         </is>
       </c>
       <c r="AT9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
@@ -2265,7 +2295,7 @@
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
@@ -2273,17 +2303,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR10" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS10" t="inlineStr">
         <is>
           <t>SER_NO_FHI_303_MONTHLY</t>
         </is>
       </c>
       <c r="AT10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV10" t="inlineStr">
@@ -2499,7 +2534,7 @@
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
@@ -2507,17 +2542,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR11" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS11" t="inlineStr">
         <is>
           <t>SER_NO_FHI_303_MONTHLY</t>
         </is>
       </c>
       <c r="AT11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
@@ -2806,7 +2846,7 @@
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
@@ -2814,17 +2854,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR13" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS13" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1220</t>
         </is>
       </c>
       <c r="AT13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV13" t="inlineStr">
@@ -3040,7 +3085,7 @@
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
@@ -3048,17 +3093,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR14" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS14" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1220</t>
         </is>
       </c>
       <c r="AT14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV14" t="inlineStr">
@@ -3199,7 +3249,7 @@
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
@@ -3207,17 +3257,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR15" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS15" t="inlineStr">
         <is>
           <t>SER_NO_FHI_303_MONTHLY</t>
         </is>
       </c>
       <c r="AT15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV15" t="inlineStr">
@@ -3433,7 +3488,7 @@
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
@@ -3441,17 +3496,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR16" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS16" t="inlineStr">
         <is>
           <t>SER_NO_FHI_303_MONTHLY</t>
         </is>
       </c>
       <c r="AT16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
@@ -3740,7 +3800,7 @@
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
@@ -3748,17 +3808,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR18" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS18" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1220</t>
         </is>
       </c>
       <c r="AT18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV18" t="inlineStr">
@@ -3974,7 +4039,7 @@
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
@@ -3982,17 +4047,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR19" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS19" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1220</t>
         </is>
       </c>
       <c r="AT19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU19" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV19" t="inlineStr">
@@ -4133,7 +4203,7 @@
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
@@ -4141,17 +4211,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR20" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS20" t="inlineStr">
         <is>
           <t>SER_NO_FHI_303_MONTHLY</t>
         </is>
       </c>
       <c r="AT20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU20" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV20" t="inlineStr">
@@ -4367,7 +4442,7 @@
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
@@ -4375,17 +4450,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR21" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS21" t="inlineStr">
         <is>
           <t>SER_NO_FHI_303_MONTHLY</t>
         </is>
       </c>
       <c r="AT21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU21" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV21" t="inlineStr">
@@ -4674,7 +4754,7 @@
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
@@ -4682,17 +4762,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR23" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS23" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1220</t>
         </is>
       </c>
       <c r="AT23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU23" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV23" t="inlineStr">
@@ -4908,7 +4993,7 @@
       </c>
       <c r="AP24" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ24" t="inlineStr">
@@ -4916,17 +5001,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR24" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS24" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1220</t>
         </is>
       </c>
       <c r="AT24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU24" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV24" t="inlineStr">
@@ -5067,7 +5157,7 @@
       </c>
       <c r="AP25" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ25" t="inlineStr">
@@ -5075,17 +5165,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR25" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS25" t="inlineStr">
         <is>
           <t>SER_NO_FHI_303_MONTHLY</t>
         </is>
       </c>
       <c r="AT25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU25" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV25" t="inlineStr">
@@ -5301,7 +5396,7 @@
       </c>
       <c r="AP26" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ26" t="inlineStr">
@@ -5309,17 +5404,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR26" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS26" t="inlineStr">
         <is>
           <t>SER_NO_FHI_303_MONTHLY</t>
         </is>
       </c>
       <c r="AT26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU26" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV26" t="inlineStr">
@@ -5608,7 +5708,7 @@
       </c>
       <c r="AP28" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ28" t="inlineStr">
@@ -5616,17 +5716,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR28" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS28" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1220</t>
         </is>
       </c>
       <c r="AT28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU28" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV28" t="inlineStr">
@@ -5842,7 +5947,7 @@
       </c>
       <c r="AP29" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ29" t="inlineStr">
@@ -5850,17 +5955,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR29" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS29" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1220</t>
         </is>
       </c>
       <c r="AT29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU29" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV29" t="inlineStr">
@@ -6001,7 +6111,7 @@
       </c>
       <c r="AP30" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ30" t="inlineStr">
@@ -6009,17 +6119,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR30" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS30" t="inlineStr">
         <is>
           <t>SER_NO_FHI_303_MONTHLY</t>
         </is>
       </c>
       <c r="AT30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU30" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV30" t="inlineStr">
@@ -6235,7 +6350,7 @@
       </c>
       <c r="AP31" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ31" t="inlineStr">
@@ -6243,17 +6358,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR31" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS31" t="inlineStr">
         <is>
           <t>SER_NO_FHI_303_MONTHLY</t>
         </is>
       </c>
       <c r="AT31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU31" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV31" t="inlineStr">
@@ -6542,7 +6662,7 @@
       </c>
       <c r="AP33" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ33" t="inlineStr">
@@ -6550,17 +6670,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR33" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS33" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1220</t>
         </is>
       </c>
       <c r="AT33" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU33" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV33" t="inlineStr">
@@ -6776,7 +6901,7 @@
       </c>
       <c r="AP34" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ34" t="inlineStr">
@@ -6784,17 +6909,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR34" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS34" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1220</t>
         </is>
       </c>
       <c r="AT34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU34" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV34" t="inlineStr">
@@ -6935,7 +7065,7 @@
       </c>
       <c r="AP35" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ35" t="inlineStr">
@@ -6943,17 +7073,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR35" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS35" t="inlineStr">
         <is>
           <t>SER_NO_FHI_303_MONTHLY</t>
         </is>
       </c>
       <c r="AT35" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU35" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV35" t="inlineStr">
@@ -7169,7 +7304,7 @@
       </c>
       <c r="AP36" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ36" t="inlineStr">
@@ -7177,17 +7312,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR36" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS36" t="inlineStr">
         <is>
           <t>SER_NO_FHI_303_MONTHLY</t>
         </is>
       </c>
       <c r="AT36" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU36" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV36" t="inlineStr">
@@ -7476,7 +7616,7 @@
       </c>
       <c r="AP38" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ38" t="inlineStr">
@@ -7484,17 +7624,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR38" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS38" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1220</t>
         </is>
       </c>
       <c r="AT38" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU38" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV38" t="inlineStr">
@@ -7710,7 +7855,7 @@
       </c>
       <c r="AP39" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ39" t="inlineStr">
@@ -7718,17 +7863,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR39" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS39" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1220</t>
         </is>
       </c>
       <c r="AT39" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU39" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV39" t="inlineStr">
@@ -7869,7 +8019,7 @@
       </c>
       <c r="AP40" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ40" t="inlineStr">
@@ -7877,17 +8027,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR40" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS40" t="inlineStr">
         <is>
           <t>SER_NO_FHI_303_MONTHLY</t>
         </is>
       </c>
       <c r="AT40" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU40" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV40" t="inlineStr">
@@ -8103,7 +8258,7 @@
       </c>
       <c r="AP41" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ41" t="inlineStr">
@@ -8111,17 +8266,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR41" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS41" t="inlineStr">
         <is>
           <t>SER_NO_FHI_303_MONTHLY</t>
         </is>
       </c>
       <c r="AT41" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU41" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV41" t="inlineStr">
@@ -8410,7 +8570,7 @@
       </c>
       <c r="AP43" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ43" t="inlineStr">
@@ -8418,17 +8578,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR43" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS43" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1220</t>
         </is>
       </c>
       <c r="AT43" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU43" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV43" t="inlineStr">
@@ -8644,7 +8809,7 @@
       </c>
       <c r="AP44" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ44" t="inlineStr">
@@ -8652,17 +8817,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR44" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS44" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1220</t>
         </is>
       </c>
       <c r="AT44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU44" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV44" t="inlineStr">
@@ -8803,7 +8973,7 @@
       </c>
       <c r="AP45" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ45" t="inlineStr">
@@ -8811,17 +8981,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR45" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS45" t="inlineStr">
         <is>
           <t>SER_NO_FHI_303_MONTHLY</t>
         </is>
       </c>
       <c r="AT45" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU45" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV45" t="inlineStr">
@@ -9037,7 +9212,7 @@
       </c>
       <c r="AP46" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ46" t="inlineStr">
@@ -9045,17 +9220,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR46" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS46" t="inlineStr">
         <is>
           <t>SER_NO_FHI_303_MONTHLY</t>
         </is>
       </c>
       <c r="AT46" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU46" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV46" t="inlineStr">
@@ -9344,7 +9524,7 @@
       </c>
       <c r="AP48" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ48" t="inlineStr">
@@ -9352,17 +9532,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR48" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS48" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1220</t>
         </is>
       </c>
       <c r="AT48" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU48" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV48" t="inlineStr">
@@ -9578,7 +9763,7 @@
       </c>
       <c r="AP49" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ49" t="inlineStr">
@@ -9586,17 +9771,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR49" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS49" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1220</t>
         </is>
       </c>
       <c r="AT49" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU49" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV49" t="inlineStr">
@@ -9737,7 +9927,7 @@
       </c>
       <c r="AP50" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ50" t="inlineStr">
@@ -9745,17 +9935,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR50" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS50" t="inlineStr">
         <is>
           <t>SER_NO_FHI_303_MONTHLY</t>
         </is>
       </c>
       <c r="AT50" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU50" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV50" t="inlineStr">
@@ -9971,7 +10166,7 @@
       </c>
       <c r="AP51" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ51" t="inlineStr">
@@ -9979,17 +10174,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR51" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS51" t="inlineStr">
         <is>
           <t>SER_NO_FHI_303_MONTHLY</t>
         </is>
       </c>
       <c r="AT51" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU51" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV51" t="inlineStr">
@@ -10278,7 +10478,7 @@
       </c>
       <c r="AP53" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ53" t="inlineStr">
@@ -10286,17 +10486,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR53" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS53" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1220</t>
         </is>
       </c>
       <c r="AT53" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU53" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV53" t="inlineStr">
@@ -10512,7 +10717,7 @@
       </c>
       <c r="AP54" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ54" t="inlineStr">
@@ -10520,17 +10725,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR54" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS54" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1220</t>
         </is>
       </c>
       <c r="AT54" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU54" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV54" t="inlineStr">
@@ -10671,7 +10881,7 @@
       </c>
       <c r="AP55" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ55" t="inlineStr">
@@ -10679,17 +10889,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR55" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS55" t="inlineStr">
         <is>
           <t>SER_NO_FHI_303_MONTHLY</t>
         </is>
       </c>
       <c r="AT55" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU55" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV55" t="inlineStr">
@@ -10905,7 +11120,7 @@
       </c>
       <c r="AP56" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ56" t="inlineStr">
@@ -10913,17 +11128,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR56" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS56" t="inlineStr">
         <is>
           <t>SER_NO_FHI_303_MONTHLY</t>
         </is>
       </c>
       <c r="AT56" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU56" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV56" t="inlineStr">
@@ -11212,7 +11432,7 @@
       </c>
       <c r="AP58" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ58" t="inlineStr">
@@ -11220,17 +11440,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR58" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS58" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1220</t>
         </is>
       </c>
       <c r="AT58" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU58" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV58" t="inlineStr">
@@ -11446,7 +11671,7 @@
       </c>
       <c r="AP59" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ59" t="inlineStr">
@@ -11454,17 +11679,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR59" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS59" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1220</t>
         </is>
       </c>
       <c r="AT59" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU59" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV59" t="inlineStr">
@@ -11605,7 +11835,7 @@
       </c>
       <c r="AP60" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ60" t="inlineStr">
@@ -11613,17 +11843,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR60" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS60" t="inlineStr">
         <is>
           <t>SER_NO_FHI_303_MONTHLY</t>
         </is>
       </c>
       <c r="AT60" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU60" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV60" t="inlineStr">
@@ -11839,7 +12074,7 @@
       </c>
       <c r="AP61" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ61" t="inlineStr">
@@ -11847,17 +12082,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR61" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS61" t="inlineStr">
         <is>
           <t>SER_NO_FHI_303_MONTHLY</t>
         </is>
       </c>
       <c r="AT61" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU61" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV61" t="inlineStr">
@@ -12146,7 +12386,7 @@
       </c>
       <c r="AP63" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ63" t="inlineStr">
@@ -12154,17 +12394,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR63" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS63" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1220</t>
         </is>
       </c>
       <c r="AT63" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU63" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV63" t="inlineStr">
@@ -12380,7 +12625,7 @@
       </c>
       <c r="AP64" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ64" t="inlineStr">
@@ -12388,17 +12633,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR64" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS64" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1220</t>
         </is>
       </c>
       <c r="AT64" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU64" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV64" t="inlineStr">
@@ -12539,7 +12789,7 @@
       </c>
       <c r="AP65" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ65" t="inlineStr">
@@ -12547,17 +12797,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR65" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS65" t="inlineStr">
         <is>
           <t>SER_NO_FHI_303_MONTHLY</t>
         </is>
       </c>
       <c r="AT65" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU65" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV65" t="inlineStr">
@@ -12773,7 +13028,7 @@
       </c>
       <c r="AP66" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ66" t="inlineStr">
@@ -12781,17 +13036,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR66" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS66" t="inlineStr">
         <is>
           <t>SER_NO_FHI_303_MONTHLY</t>
         </is>
       </c>
       <c r="AT66" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU66" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV66" t="inlineStr">
@@ -13080,7 +13340,7 @@
       </c>
       <c r="AP68" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ68" t="inlineStr">
@@ -13088,17 +13348,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR68" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS68" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1220</t>
         </is>
       </c>
       <c r="AT68" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU68" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV68" t="inlineStr">
@@ -13314,7 +13579,7 @@
       </c>
       <c r="AP69" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ69" t="inlineStr">
@@ -13322,17 +13587,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR69" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS69" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1220</t>
         </is>
       </c>
       <c r="AT69" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU69" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV69" t="inlineStr">
@@ -13473,7 +13743,7 @@
       </c>
       <c r="AP70" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ70" t="inlineStr">
@@ -13481,17 +13751,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR70" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS70" t="inlineStr">
         <is>
           <t>SER_NO_FHI_303_MONTHLY</t>
         </is>
       </c>
       <c r="AT70" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU70" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV70" t="inlineStr">
@@ -13707,7 +13982,7 @@
       </c>
       <c r="AP71" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ71" t="inlineStr">
@@ -13715,17 +13990,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR71" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS71" t="inlineStr">
         <is>
           <t>SER_NO_FHI_303_MONTHLY</t>
         </is>
       </c>
       <c r="AT71" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU71" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV71" t="inlineStr">
@@ -14014,7 +14294,7 @@
       </c>
       <c r="AP73" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ73" t="inlineStr">
@@ -14022,17 +14302,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR73" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS73" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1220</t>
         </is>
       </c>
       <c r="AT73" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU73" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV73" t="inlineStr">
@@ -14248,7 +14533,7 @@
       </c>
       <c r="AP74" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ74" t="inlineStr">
@@ -14256,17 +14541,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR74" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS74" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1220</t>
         </is>
       </c>
       <c r="AT74" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU74" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV74" t="inlineStr">
@@ -14407,7 +14697,7 @@
       </c>
       <c r="AP75" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ75" t="inlineStr">
@@ -14415,17 +14705,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR75" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS75" t="inlineStr">
         <is>
           <t>SER_NO_FHI_303_MONTHLY</t>
         </is>
       </c>
       <c r="AT75" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU75" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV75" t="inlineStr">
@@ -14641,7 +14936,7 @@
       </c>
       <c r="AP76" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ76" t="inlineStr">
@@ -14649,17 +14944,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR76" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS76" t="inlineStr">
         <is>
           <t>SER_NO_FHI_303_MONTHLY</t>
         </is>
       </c>
       <c r="AT76" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU76" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV76" t="inlineStr">
@@ -14948,7 +15248,7 @@
       </c>
       <c r="AP78" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ78" t="inlineStr">
@@ -14956,17 +15256,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR78" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS78" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1220</t>
         </is>
       </c>
       <c r="AT78" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU78" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV78" t="inlineStr">
@@ -15182,7 +15487,7 @@
       </c>
       <c r="AP79" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ79" t="inlineStr">
@@ -15190,17 +15495,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR79" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS79" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1220</t>
         </is>
       </c>
       <c r="AT79" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU79" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV79" t="inlineStr">
@@ -15341,7 +15651,7 @@
       </c>
       <c r="AP80" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ80" t="inlineStr">
@@ -15349,17 +15659,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR80" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS80" t="inlineStr">
         <is>
           <t>SER_NO_FHI_303_MONTHLY</t>
         </is>
       </c>
       <c r="AT80" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU80" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV80" t="inlineStr">
@@ -15575,7 +15890,7 @@
       </c>
       <c r="AP81" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ81" t="inlineStr">
@@ -15583,17 +15898,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR81" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS81" t="inlineStr">
         <is>
           <t>SER_NO_FHI_303_MONTHLY</t>
         </is>
       </c>
       <c r="AT81" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU81" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV81" t="inlineStr">
@@ -15882,7 +16202,7 @@
       </c>
       <c r="AP83" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ83" t="inlineStr">
@@ -15890,17 +16210,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR83" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS83" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1220</t>
         </is>
       </c>
       <c r="AT83" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU83" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV83" t="inlineStr">
@@ -16116,7 +16441,7 @@
       </c>
       <c r="AP84" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ84" t="inlineStr">
@@ -16124,17 +16449,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR84" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS84" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1220</t>
         </is>
       </c>
       <c r="AT84" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU84" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV84" t="inlineStr">
@@ -16275,7 +16605,7 @@
       </c>
       <c r="AP85" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ85" t="inlineStr">
@@ -16283,17 +16613,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR85" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS85" t="inlineStr">
         <is>
           <t>SER_NO_FHI_303_MONTHLY</t>
         </is>
       </c>
       <c r="AT85" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU85" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV85" t="inlineStr">
@@ -16509,7 +16844,7 @@
       </c>
       <c r="AP86" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ86" t="inlineStr">
@@ -16517,17 +16852,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR86" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS86" t="inlineStr">
         <is>
           <t>SER_NO_FHI_303_MONTHLY</t>
         </is>
       </c>
       <c r="AT86" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU86" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV86" t="inlineStr">
@@ -16816,7 +17156,7 @@
       </c>
       <c r="AP88" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ88" t="inlineStr">
@@ -16824,17 +17164,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR88" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS88" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1220</t>
         </is>
       </c>
       <c r="AT88" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU88" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV88" t="inlineStr">
@@ -17050,7 +17395,7 @@
       </c>
       <c r="AP89" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ89" t="inlineStr">
@@ -17058,17 +17403,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR89" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS89" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1220</t>
         </is>
       </c>
       <c r="AT89" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU89" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV89" t="inlineStr">
@@ -17209,7 +17559,7 @@
       </c>
       <c r="AP90" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ90" t="inlineStr">
@@ -17217,17 +17567,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR90" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS90" t="inlineStr">
         <is>
           <t>SER_NO_FHI_303_MONTHLY</t>
         </is>
       </c>
       <c r="AT90" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU90" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV90" t="inlineStr">
@@ -17443,7 +17798,7 @@
       </c>
       <c r="AP91" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ91" t="inlineStr">
@@ -17451,17 +17806,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR91" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS91" t="inlineStr">
         <is>
           <t>SER_NO_FHI_303_MONTHLY</t>
         </is>
       </c>
       <c r="AT91" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU91" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV91" t="inlineStr">
@@ -17750,7 +18110,7 @@
       </c>
       <c r="AP93" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ93" t="inlineStr">
@@ -17758,17 +18118,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR93" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS93" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1220</t>
         </is>
       </c>
       <c r="AT93" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU93" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV93" t="inlineStr">
@@ -17984,7 +18349,7 @@
       </c>
       <c r="AP94" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ94" t="inlineStr">
@@ -17992,17 +18357,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR94" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS94" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1220</t>
         </is>
       </c>
       <c r="AT94" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU94" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV94" t="inlineStr">
@@ -18143,7 +18513,7 @@
       </c>
       <c r="AP95" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ95" t="inlineStr">
@@ -18151,17 +18521,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR95" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS95" t="inlineStr">
         <is>
           <t>SER_NO_FHI_303_MONTHLY</t>
         </is>
       </c>
       <c r="AT95" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU95" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV95" t="inlineStr">
@@ -18377,7 +18752,7 @@
       </c>
       <c r="AP96" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ96" t="inlineStr">
@@ -18385,17 +18760,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR96" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS96" t="inlineStr">
         <is>
           <t>SER_NO_FHI_303_MONTHLY</t>
         </is>
       </c>
       <c r="AT96" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU96" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV96" t="inlineStr">
@@ -18684,7 +19064,7 @@
       </c>
       <c r="AP98" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ98" t="inlineStr">
@@ -18692,17 +19072,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR98" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS98" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1220</t>
         </is>
       </c>
       <c r="AT98" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU98" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV98" t="inlineStr">
@@ -18918,7 +19303,7 @@
       </c>
       <c r="AP99" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ99" t="inlineStr">
@@ -18926,17 +19311,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR99" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS99" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1220</t>
         </is>
       </c>
       <c r="AT99" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU99" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV99" t="inlineStr">
@@ -19077,7 +19467,7 @@
       </c>
       <c r="AP100" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ100" t="inlineStr">
@@ -19085,17 +19475,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR100" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS100" t="inlineStr">
         <is>
           <t>SER_NO_FHI_303_MONTHLY</t>
         </is>
       </c>
       <c r="AT100" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU100" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV100" t="inlineStr">
@@ -19311,7 +19706,7 @@
       </c>
       <c r="AP101" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ101" t="inlineStr">
@@ -19319,17 +19714,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR101" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS101" t="inlineStr">
         <is>
           <t>SER_NO_FHI_303_MONTHLY</t>
         </is>
       </c>
       <c r="AT101" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU101" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV101" t="inlineStr">
@@ -19618,7 +20018,7 @@
       </c>
       <c r="AP103" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ103" t="inlineStr">
@@ -19626,17 +20026,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR103" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS103" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1220</t>
         </is>
       </c>
       <c r="AT103" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU103" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV103" t="inlineStr">
@@ -19852,7 +20257,7 @@
       </c>
       <c r="AP104" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ104" t="inlineStr">
@@ -19860,17 +20265,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR104" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS104" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1220</t>
         </is>
       </c>
       <c r="AT104" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU104" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV104" t="inlineStr">
@@ -20011,7 +20421,7 @@
       </c>
       <c r="AP105" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ105" t="inlineStr">
@@ -20019,17 +20429,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR105" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS105" t="inlineStr">
         <is>
           <t>SER_NO_FHI_303_MONTHLY</t>
         </is>
       </c>
       <c r="AT105" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU105" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV105" t="inlineStr">
@@ -20245,7 +20660,7 @@
       </c>
       <c r="AP106" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ106" t="inlineStr">
@@ -20253,17 +20668,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR106" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS106" t="inlineStr">
         <is>
           <t>SER_NO_FHI_303_MONTHLY</t>
         </is>
       </c>
       <c r="AT106" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU106" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV106" t="inlineStr">
@@ -20552,7 +20972,7 @@
       </c>
       <c r="AP108" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ108" t="inlineStr">
@@ -20560,17 +20980,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR108" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS108" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1220</t>
         </is>
       </c>
       <c r="AT108" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU108" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV108" t="inlineStr">
@@ -20786,7 +21211,7 @@
       </c>
       <c r="AP109" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ109" t="inlineStr">
@@ -20794,17 +21219,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR109" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS109" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1220</t>
         </is>
       </c>
       <c r="AT109" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU109" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV109" t="inlineStr">
@@ -20945,7 +21375,7 @@
       </c>
       <c r="AP110" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ110" t="inlineStr">
@@ -20953,17 +21383,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR110" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS110" t="inlineStr">
         <is>
           <t>SER_NO_FHI_303_MONTHLY</t>
         </is>
       </c>
       <c r="AT110" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU110" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV110" t="inlineStr">
@@ -21179,7 +21614,7 @@
       </c>
       <c r="AP111" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ111" t="inlineStr">
@@ -21187,17 +21622,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR111" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS111" t="inlineStr">
         <is>
           <t>SER_NO_FHI_303_MONTHLY</t>
         </is>
       </c>
       <c r="AT111" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU111" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV111" t="inlineStr">
@@ -21486,7 +21926,7 @@
       </c>
       <c r="AP113" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ113" t="inlineStr">
@@ -21494,17 +21934,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR113" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS113" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1220</t>
         </is>
       </c>
       <c r="AT113" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU113" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV113" t="inlineStr">
@@ -21720,7 +22165,7 @@
       </c>
       <c r="AP114" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ114" t="inlineStr">
@@ -21728,17 +22173,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR114" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS114" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1220</t>
         </is>
       </c>
       <c r="AT114" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU114" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV114" t="inlineStr">
@@ -21879,7 +22329,7 @@
       </c>
       <c r="AP115" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ115" t="inlineStr">
@@ -21887,17 +22337,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR115" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS115" t="inlineStr">
         <is>
           <t>SER_NO_FHI_303_MONTHLY</t>
         </is>
       </c>
       <c r="AT115" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU115" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV115" t="inlineStr">
@@ -22113,7 +22568,7 @@
       </c>
       <c r="AP116" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ116" t="inlineStr">
@@ -22121,17 +22576,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR116" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS116" t="inlineStr">
         <is>
           <t>SER_NO_FHI_303_MONTHLY</t>
         </is>
       </c>
       <c r="AT116" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU116" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV116" t="inlineStr">
@@ -22420,7 +22880,7 @@
       </c>
       <c r="AP118" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ118" t="inlineStr">
@@ -22428,17 +22888,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR118" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS118" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1220</t>
         </is>
       </c>
       <c r="AT118" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU118" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV118" t="inlineStr">
@@ -22654,7 +23119,7 @@
       </c>
       <c r="AP119" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ119" t="inlineStr">
@@ -22662,17 +23127,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR119" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS119" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1220</t>
         </is>
       </c>
       <c r="AT119" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU119" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV119" t="inlineStr">
@@ -22813,7 +23283,7 @@
       </c>
       <c r="AP120" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ120" t="inlineStr">
@@ -22821,17 +23291,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR120" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS120" t="inlineStr">
         <is>
           <t>SER_NO_FHI_303_MONTHLY</t>
         </is>
       </c>
       <c r="AT120" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU120" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV120" t="inlineStr">
@@ -23047,7 +23522,7 @@
       </c>
       <c r="AP121" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ121" t="inlineStr">
@@ -23055,17 +23530,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR121" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS121" t="inlineStr">
         <is>
           <t>SER_NO_FHI_303_MONTHLY</t>
         </is>
       </c>
       <c r="AT121" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU121" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV121" t="inlineStr">
@@ -23354,7 +23834,7 @@
       </c>
       <c r="AP123" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ123" t="inlineStr">
@@ -23362,17 +23842,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR123" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS123" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1220</t>
         </is>
       </c>
       <c r="AT123" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU123" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV123" t="inlineStr">
@@ -23588,7 +24073,7 @@
       </c>
       <c r="AP124" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ124" t="inlineStr">
@@ -23596,17 +24081,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR124" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS124" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1220</t>
         </is>
       </c>
       <c r="AT124" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU124" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV124" t="inlineStr">
@@ -23747,7 +24237,7 @@
       </c>
       <c r="AP125" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ125" t="inlineStr">
@@ -23755,17 +24245,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR125" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS125" t="inlineStr">
         <is>
           <t>SER_NO_FHI_303_MONTHLY</t>
         </is>
       </c>
       <c r="AT125" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU125" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV125" t="inlineStr">
@@ -23981,7 +24476,7 @@
       </c>
       <c r="AP126" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ126" t="inlineStr">
@@ -23989,17 +24484,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR126" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS126" t="inlineStr">
         <is>
           <t>SER_NO_FHI_303_MONTHLY</t>
         </is>
       </c>
       <c r="AT126" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU126" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV126" t="inlineStr">
@@ -24288,7 +24788,7 @@
       </c>
       <c r="AP128" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ128" t="inlineStr">
@@ -24296,17 +24796,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR128" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS128" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1220</t>
         </is>
       </c>
       <c r="AT128" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU128" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV128" t="inlineStr">
@@ -24522,7 +25027,7 @@
       </c>
       <c r="AP129" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ129" t="inlineStr">
@@ -24530,17 +25035,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR129" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS129" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1220</t>
         </is>
       </c>
       <c r="AT129" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU129" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV129" t="inlineStr">
@@ -24681,7 +25191,7 @@
       </c>
       <c r="AP130" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ130" t="inlineStr">
@@ -24689,17 +25199,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR130" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS130" t="inlineStr">
         <is>
           <t>SER_NO_FHI_303_MONTHLY</t>
         </is>
       </c>
       <c r="AT130" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU130" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV130" t="inlineStr">
@@ -24915,7 +25430,7 @@
       </c>
       <c r="AP131" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ131" t="inlineStr">
@@ -24923,17 +25438,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR131" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS131" t="inlineStr">
         <is>
           <t>SER_NO_FHI_303_MONTHLY</t>
         </is>
       </c>
       <c r="AT131" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU131" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV131" t="inlineStr">
@@ -25222,7 +25742,7 @@
       </c>
       <c r="AP133" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ133" t="inlineStr">
@@ -25230,17 +25750,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR133" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS133" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1220</t>
         </is>
       </c>
       <c r="AT133" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU133" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV133" t="inlineStr">
@@ -25456,7 +25981,7 @@
       </c>
       <c r="AP134" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ134" t="inlineStr">
@@ -25464,17 +25989,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR134" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS134" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1220</t>
         </is>
       </c>
       <c r="AT134" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU134" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV134" t="inlineStr">
@@ -25615,7 +26145,7 @@
       </c>
       <c r="AP135" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ135" t="inlineStr">
@@ -25623,17 +26153,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR135" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS135" t="inlineStr">
         <is>
           <t>SER_NO_FHI_303_MONTHLY</t>
         </is>
       </c>
       <c r="AT135" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU135" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV135" t="inlineStr">
@@ -25849,7 +26384,7 @@
       </c>
       <c r="AP136" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ136" t="inlineStr">
@@ -25857,17 +26392,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR136" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS136" t="inlineStr">
         <is>
           <t>SER_NO_FHI_303_MONTHLY</t>
         </is>
       </c>
       <c r="AT136" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU136" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV136" t="inlineStr">
@@ -26156,7 +26696,7 @@
       </c>
       <c r="AP138" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ138" t="inlineStr">
@@ -26164,17 +26704,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR138" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS138" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1220</t>
         </is>
       </c>
       <c r="AT138" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU138" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV138" t="inlineStr">
@@ -26390,7 +26935,7 @@
       </c>
       <c r="AP139" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ139" t="inlineStr">
@@ -26398,17 +26943,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR139" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS139" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1220</t>
         </is>
       </c>
       <c r="AT139" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU139" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV139" t="inlineStr">
@@ -26549,7 +27099,7 @@
       </c>
       <c r="AP140" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ140" t="inlineStr">
@@ -26557,17 +27107,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR140" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS140" t="inlineStr">
         <is>
           <t>SER_NO_FHI_303_MONTHLY</t>
         </is>
       </c>
       <c r="AT140" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU140" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV140" t="inlineStr">
@@ -26783,7 +27338,7 @@
       </c>
       <c r="AP141" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ141" t="inlineStr">
@@ -26791,17 +27346,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR141" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS141" t="inlineStr">
         <is>
           <t>SER_NO_FHI_303_MONTHLY</t>
         </is>
       </c>
       <c r="AT141" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU141" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV141" t="inlineStr">
@@ -27090,7 +27650,7 @@
       </c>
       <c r="AP143" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ143" t="inlineStr">
@@ -27098,17 +27658,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR143" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS143" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1220</t>
         </is>
       </c>
       <c r="AT143" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU143" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV143" t="inlineStr">
@@ -27324,7 +27889,7 @@
       </c>
       <c r="AP144" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ144" t="inlineStr">
@@ -27332,17 +27897,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR144" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS144" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1220</t>
         </is>
       </c>
       <c r="AT144" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU144" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV144" t="inlineStr">
@@ -27483,7 +28053,7 @@
       </c>
       <c r="AP145" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ145" t="inlineStr">
@@ -27491,17 +28061,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR145" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS145" t="inlineStr">
         <is>
           <t>SER_NO_FHI_303_MONTHLY</t>
         </is>
       </c>
       <c r="AT145" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU145" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV145" t="inlineStr">
@@ -27717,7 +28292,7 @@
       </c>
       <c r="AP146" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ146" t="inlineStr">
@@ -27725,17 +28300,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR146" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS146" t="inlineStr">
         <is>
           <t>SER_NO_FHI_303_MONTHLY</t>
         </is>
       </c>
       <c r="AT146" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU146" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV146" t="inlineStr">
@@ -28024,7 +28604,7 @@
       </c>
       <c r="AP148" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ148" t="inlineStr">
@@ -28032,17 +28612,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR148" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS148" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1220</t>
         </is>
       </c>
       <c r="AT148" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU148" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV148" t="inlineStr">
@@ -28258,7 +28843,7 @@
       </c>
       <c r="AP149" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ149" t="inlineStr">
@@ -28266,17 +28851,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR149" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS149" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1220</t>
         </is>
       </c>
       <c r="AT149" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU149" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV149" t="inlineStr">
@@ -28417,7 +29007,7 @@
       </c>
       <c r="AP150" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ150" t="inlineStr">
@@ -28425,17 +29015,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR150" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS150" t="inlineStr">
         <is>
           <t>SER_NO_FHI_303_MONTHLY</t>
         </is>
       </c>
       <c r="AT150" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU150" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV150" t="inlineStr">
@@ -28651,7 +29246,7 @@
       </c>
       <c r="AP151" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ151" t="inlineStr">
@@ -28659,17 +29254,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR151" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS151" t="inlineStr">
         <is>
           <t>SER_NO_FHI_303_MONTHLY</t>
         </is>
       </c>
       <c r="AT151" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU151" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV151" t="inlineStr">
@@ -28958,7 +29558,7 @@
       </c>
       <c r="AP153" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ153" t="inlineStr">
@@ -28966,17 +29566,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR153" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS153" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1220</t>
         </is>
       </c>
       <c r="AT153" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU153" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV153" t="inlineStr">
@@ -29192,7 +29797,7 @@
       </c>
       <c r="AP154" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ154" t="inlineStr">
@@ -29200,17 +29805,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR154" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS154" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1220</t>
         </is>
       </c>
       <c r="AT154" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU154" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV154" t="inlineStr">
@@ -29351,7 +29961,7 @@
       </c>
       <c r="AP155" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ155" t="inlineStr">
@@ -29359,17 +29969,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR155" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS155" t="inlineStr">
         <is>
           <t>SER_NO_FHI_303_MONTHLY</t>
         </is>
       </c>
       <c r="AT155" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU155" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV155" t="inlineStr">
@@ -29585,7 +30200,7 @@
       </c>
       <c r="AP156" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ156" t="inlineStr">
@@ -29593,17 +30208,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR156" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS156" t="inlineStr">
         <is>
           <t>SER_NO_FHI_303_MONTHLY</t>
         </is>
       </c>
       <c r="AT156" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU156" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV156" t="inlineStr">
@@ -29892,7 +30512,7 @@
       </c>
       <c r="AP158" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ158" t="inlineStr">
@@ -29900,17 +30520,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR158" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS158" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1220</t>
         </is>
       </c>
       <c r="AT158" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU158" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV158" t="inlineStr">
@@ -30126,7 +30751,7 @@
       </c>
       <c r="AP159" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ159" t="inlineStr">
@@ -30134,17 +30759,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR159" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS159" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1220</t>
         </is>
       </c>
       <c r="AT159" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU159" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV159" t="inlineStr">
@@ -30285,7 +30915,7 @@
       </c>
       <c r="AP160" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ160" t="inlineStr">
@@ -30293,17 +30923,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR160" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS160" t="inlineStr">
         <is>
           <t>SER_NO_FHI_303_MONTHLY</t>
         </is>
       </c>
       <c r="AT160" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU160" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV160" t="inlineStr">
@@ -30519,7 +31154,7 @@
       </c>
       <c r="AP161" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ161" t="inlineStr">
@@ -30527,17 +31162,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR161" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS161" t="inlineStr">
         <is>
           <t>SER_NO_FHI_303_MONTHLY</t>
         </is>
       </c>
       <c r="AT161" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU161" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV161" t="inlineStr">
@@ -30826,7 +31466,7 @@
       </c>
       <c r="AP163" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ163" t="inlineStr">
@@ -30834,17 +31474,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR163" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS163" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1220</t>
         </is>
       </c>
       <c r="AT163" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU163" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV163" t="inlineStr">
@@ -31060,7 +31705,7 @@
       </c>
       <c r="AP164" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ164" t="inlineStr">
@@ -31068,17 +31713,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR164" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS164" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1220</t>
         </is>
       </c>
       <c r="AT164" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU164" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV164" t="inlineStr">
@@ -31219,7 +31869,7 @@
       </c>
       <c r="AP165" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ165" t="inlineStr">
@@ -31227,17 +31877,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR165" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS165" t="inlineStr">
         <is>
           <t>SER_NO_FHI_303_MONTHLY</t>
         </is>
       </c>
       <c r="AT165" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU165" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV165" t="inlineStr">
@@ -31453,7 +32108,7 @@
       </c>
       <c r="AP166" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ166" t="inlineStr">
@@ -31461,17 +32116,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR166" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS166" t="inlineStr">
         <is>
           <t>SER_NO_FHI_303_MONTHLY</t>
         </is>
       </c>
       <c r="AT166" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU166" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV166" t="inlineStr">
@@ -31760,7 +32420,7 @@
       </c>
       <c r="AP168" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ168" t="inlineStr">
@@ -31768,17 +32428,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR168" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS168" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1220</t>
         </is>
       </c>
       <c r="AT168" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU168" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV168" t="inlineStr">
@@ -31994,7 +32659,7 @@
       </c>
       <c r="AP169" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ169" t="inlineStr">
@@ -32002,17 +32667,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR169" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS169" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1220</t>
         </is>
       </c>
       <c r="AT169" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU169" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV169" t="inlineStr">
@@ -32153,7 +32823,7 @@
       </c>
       <c r="AP170" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ170" t="inlineStr">
@@ -32161,17 +32831,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR170" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS170" t="inlineStr">
         <is>
           <t>SER_NO_FHI_303_MONTHLY</t>
         </is>
       </c>
       <c r="AT170" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU170" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV170" t="inlineStr">
@@ -32387,7 +33062,7 @@
       </c>
       <c r="AP171" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ171" t="inlineStr">
@@ -32395,17 +33070,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR171" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS171" t="inlineStr">
         <is>
           <t>SER_NO_FHI_303_MONTHLY</t>
         </is>
       </c>
       <c r="AT171" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU171" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV171" t="inlineStr">
@@ -32694,7 +33374,7 @@
       </c>
       <c r="AP173" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ173" t="inlineStr">
@@ -32702,17 +33382,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR173" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS173" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1220</t>
         </is>
       </c>
       <c r="AT173" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU173" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV173" t="inlineStr">
@@ -32928,7 +33613,7 @@
       </c>
       <c r="AP174" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ174" t="inlineStr">
@@ -32936,17 +33621,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR174" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS174" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1220</t>
         </is>
       </c>
       <c r="AT174" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU174" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV174" t="inlineStr">
@@ -33087,7 +33777,7 @@
       </c>
       <c r="AP175" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ175" t="inlineStr">
@@ -33095,17 +33785,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR175" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS175" t="inlineStr">
         <is>
           <t>SER_NO_FHI_303_MONTHLY</t>
         </is>
       </c>
       <c r="AT175" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU175" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV175" t="inlineStr">
@@ -33321,7 +34016,7 @@
       </c>
       <c r="AP176" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ176" t="inlineStr">
@@ -33329,17 +34024,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR176" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS176" t="inlineStr">
         <is>
           <t>SER_NO_FHI_303_MONTHLY</t>
         </is>
       </c>
       <c r="AT176" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU176" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV176" t="inlineStr">
@@ -33628,7 +34328,7 @@
       </c>
       <c r="AP178" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ178" t="inlineStr">
@@ -33636,17 +34336,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR178" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS178" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1220</t>
         </is>
       </c>
       <c r="AT178" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU178" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV178" t="inlineStr">
@@ -33862,7 +34567,7 @@
       </c>
       <c r="AP179" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ179" t="inlineStr">
@@ -33870,17 +34575,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR179" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS179" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1220</t>
         </is>
       </c>
       <c r="AT179" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU179" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV179" t="inlineStr">
@@ -34021,7 +34731,7 @@
       </c>
       <c r="AP180" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ180" t="inlineStr">
@@ -34029,17 +34739,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR180" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS180" t="inlineStr">
         <is>
           <t>SER_NO_FHI_303_MONTHLY</t>
         </is>
       </c>
       <c r="AT180" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU180" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV180" t="inlineStr">
@@ -34255,7 +34970,7 @@
       </c>
       <c r="AP181" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ181" t="inlineStr">
@@ -34263,17 +34978,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR181" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS181" t="inlineStr">
         <is>
           <t>SER_NO_FHI_303_MONTHLY</t>
         </is>
       </c>
       <c r="AT181" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU181" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV181" t="inlineStr">
@@ -34562,7 +35282,7 @@
       </c>
       <c r="AP183" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ183" t="inlineStr">
@@ -34570,17 +35290,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR183" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS183" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1220</t>
         </is>
       </c>
       <c r="AT183" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU183" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV183" t="inlineStr">
@@ -34796,7 +35521,7 @@
       </c>
       <c r="AP184" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ184" t="inlineStr">
@@ -34804,17 +35529,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR184" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS184" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1220</t>
         </is>
       </c>
       <c r="AT184" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU184" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV184" t="inlineStr">
@@ -34955,7 +35685,7 @@
       </c>
       <c r="AP185" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ185" t="inlineStr">
@@ -34963,17 +35693,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR185" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS185" t="inlineStr">
         <is>
           <t>SER_NO_FHI_303_MONTHLY</t>
         </is>
       </c>
       <c r="AT185" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU185" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV185" t="inlineStr">
@@ -35189,7 +35924,7 @@
       </c>
       <c r="AP186" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ186" t="inlineStr">
@@ -35197,17 +35932,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR186" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS186" t="inlineStr">
         <is>
           <t>SER_NO_FHI_303_MONTHLY</t>
         </is>
       </c>
       <c r="AT186" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU186" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV186" t="inlineStr">
@@ -35496,7 +36236,7 @@
       </c>
       <c r="AP188" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ188" t="inlineStr">
@@ -35504,17 +36244,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR188" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS188" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1220</t>
         </is>
       </c>
       <c r="AT188" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU188" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV188" t="inlineStr">
@@ -35730,7 +36475,7 @@
       </c>
       <c r="AP189" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ189" t="inlineStr">
@@ -35738,17 +36483,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR189" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS189" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1220</t>
         </is>
       </c>
       <c r="AT189" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU189" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV189" t="inlineStr">
@@ -35889,7 +36639,7 @@
       </c>
       <c r="AP190" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ190" t="inlineStr">
@@ -35897,17 +36647,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR190" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS190" t="inlineStr">
         <is>
           <t>SER_NO_FHI_303_MONTHLY</t>
         </is>
       </c>
       <c r="AT190" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU190" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV190" t="inlineStr">
@@ -36123,7 +36878,7 @@
       </c>
       <c r="AP191" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ191" t="inlineStr">
@@ -36131,17 +36886,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR191" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS191" t="inlineStr">
         <is>
           <t>SER_NO_FHI_303_MONTHLY</t>
         </is>
       </c>
       <c r="AT191" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU191" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV191" t="inlineStr">
@@ -36430,7 +37190,7 @@
       </c>
       <c r="AP193" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ193" t="inlineStr">
@@ -36438,17 +37198,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR193" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS193" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1220</t>
         </is>
       </c>
       <c r="AT193" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU193" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV193" t="inlineStr">
@@ -36664,7 +37429,7 @@
       </c>
       <c r="AP194" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ194" t="inlineStr">
@@ -36672,17 +37437,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR194" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS194" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1220</t>
         </is>
       </c>
       <c r="AT194" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU194" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV194" t="inlineStr">
@@ -36823,7 +37593,7 @@
       </c>
       <c r="AP195" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ195" t="inlineStr">
@@ -36831,17 +37601,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR195" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS195" t="inlineStr">
         <is>
           <t>SER_NO_FHI_303_MONTHLY</t>
         </is>
       </c>
       <c r="AT195" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU195" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV195" t="inlineStr">
@@ -37057,7 +37832,7 @@
       </c>
       <c r="AP196" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ196" t="inlineStr">
@@ -37065,17 +37840,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR196" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS196" t="inlineStr">
         <is>
           <t>SER_NO_FHI_303_MONTHLY</t>
         </is>
       </c>
       <c r="AT196" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU196" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV196" t="inlineStr">
@@ -37364,7 +38144,7 @@
       </c>
       <c r="AP198" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ198" t="inlineStr">
@@ -37372,17 +38152,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR198" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS198" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1220</t>
         </is>
       </c>
       <c r="AT198" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU198" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV198" t="inlineStr">
@@ -37598,7 +38383,7 @@
       </c>
       <c r="AP199" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ199" t="inlineStr">
@@ -37606,17 +38391,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR199" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS199" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1220</t>
         </is>
       </c>
       <c r="AT199" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU199" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV199" t="inlineStr">
@@ -37757,7 +38547,7 @@
       </c>
       <c r="AP200" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ200" t="inlineStr">
@@ -37765,17 +38555,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR200" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS200" t="inlineStr">
         <is>
           <t>SER_NO_FHI_303_MONTHLY</t>
         </is>
       </c>
       <c r="AT200" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU200" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV200" t="inlineStr">
@@ -37991,7 +38786,7 @@
       </c>
       <c r="AP201" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ201" t="inlineStr">
@@ -37999,17 +38794,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR201" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS201" t="inlineStr">
         <is>
           <t>SER_NO_FHI_303_MONTHLY</t>
         </is>
       </c>
       <c r="AT201" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU201" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV201" t="inlineStr">
@@ -38298,7 +39098,7 @@
       </c>
       <c r="AP203" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ203" t="inlineStr">
@@ -38306,17 +39106,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR203" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS203" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1220</t>
         </is>
       </c>
       <c r="AT203" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU203" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV203" t="inlineStr">
@@ -38532,7 +39337,7 @@
       </c>
       <c r="AP204" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ204" t="inlineStr">
@@ -38540,17 +39345,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR204" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS204" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1220</t>
         </is>
       </c>
       <c r="AT204" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU204" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV204" t="inlineStr">
@@ -38691,7 +39501,7 @@
       </c>
       <c r="AP205" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ205" t="inlineStr">
@@ -38699,17 +39509,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR205" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS205" t="inlineStr">
         <is>
           <t>SER_NO_FHI_303_MONTHLY</t>
         </is>
       </c>
       <c r="AT205" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU205" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV205" t="inlineStr">
@@ -38925,7 +39740,7 @@
       </c>
       <c r="AP206" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ206" t="inlineStr">
@@ -38933,17 +39748,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR206" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS206" t="inlineStr">
         <is>
           <t>SER_NO_FHI_303_MONTHLY</t>
         </is>
       </c>
       <c r="AT206" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU206" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV206" t="inlineStr">
@@ -39232,7 +40052,7 @@
       </c>
       <c r="AP208" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ208" t="inlineStr">
@@ -39240,17 +40060,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR208" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS208" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1220</t>
         </is>
       </c>
       <c r="AT208" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU208" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV208" t="inlineStr">
@@ -39466,7 +40291,7 @@
       </c>
       <c r="AP209" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ209" t="inlineStr">
@@ -39474,17 +40299,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR209" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS209" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1220</t>
         </is>
       </c>
       <c r="AT209" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU209" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV209" t="inlineStr">
@@ -39625,7 +40455,7 @@
       </c>
       <c r="AP210" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ210" t="inlineStr">
@@ -39633,17 +40463,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR210" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS210" t="inlineStr">
         <is>
           <t>SER_NO_FHI_303_MONTHLY</t>
         </is>
       </c>
       <c r="AT210" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU210" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV210" t="inlineStr">
@@ -39859,7 +40694,7 @@
       </c>
       <c r="AP211" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ211" t="inlineStr">
@@ -39867,17 +40702,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR211" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS211" t="inlineStr">
         <is>
           <t>SER_NO_FHI_303_MONTHLY</t>
         </is>
       </c>
       <c r="AT211" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU211" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV211" t="inlineStr">
@@ -40166,7 +41006,7 @@
       </c>
       <c r="AP213" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ213" t="inlineStr">
@@ -40174,17 +41014,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR213" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS213" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1220</t>
         </is>
       </c>
       <c r="AT213" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU213" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV213" t="inlineStr">
@@ -40400,7 +41245,7 @@
       </c>
       <c r="AP214" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ214" t="inlineStr">
@@ -40408,17 +41253,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR214" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS214" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1220</t>
         </is>
       </c>
       <c r="AT214" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU214" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV214" t="inlineStr">
@@ -40559,7 +41409,7 @@
       </c>
       <c r="AP215" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ215" t="inlineStr">
@@ -40567,17 +41417,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR215" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS215" t="inlineStr">
         <is>
           <t>SER_NO_FHI_303_MONTHLY</t>
         </is>
       </c>
       <c r="AT215" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU215" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV215" t="inlineStr">
@@ -40793,7 +41648,7 @@
       </c>
       <c r="AP216" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ216" t="inlineStr">
@@ -40801,17 +41656,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR216" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS216" t="inlineStr">
         <is>
           <t>SER_NO_FHI_303_MONTHLY</t>
         </is>
       </c>
       <c r="AT216" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU216" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV216" t="inlineStr">
@@ -41100,7 +41960,7 @@
       </c>
       <c r="AP218" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ218" t="inlineStr">
@@ -41108,17 +41968,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR218" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS218" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1220</t>
         </is>
       </c>
       <c r="AT218" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU218" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV218" t="inlineStr">
@@ -41334,7 +42199,7 @@
       </c>
       <c r="AP219" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ219" t="inlineStr">
@@ -41342,17 +42207,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR219" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS219" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1220</t>
         </is>
       </c>
       <c r="AT219" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU219" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV219" t="inlineStr">
@@ -41493,7 +42363,7 @@
       </c>
       <c r="AP220" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ220" t="inlineStr">
@@ -41501,17 +42371,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR220" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS220" t="inlineStr">
         <is>
           <t>SER_NO_FHI_303_MONTHLY</t>
         </is>
       </c>
       <c r="AT220" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU220" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV220" t="inlineStr">
@@ -41727,7 +42602,7 @@
       </c>
       <c r="AP221" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ221" t="inlineStr">
@@ -41735,17 +42610,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR221" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS221" t="inlineStr">
         <is>
           <t>SER_NO_FHI_303_MONTHLY</t>
         </is>
       </c>
       <c r="AT221" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU221" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV221" t="inlineStr">
@@ -42034,7 +42914,7 @@
       </c>
       <c r="AP223" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ223" t="inlineStr">
@@ -42042,17 +42922,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR223" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS223" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1220</t>
         </is>
       </c>
       <c r="AT223" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU223" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV223" t="inlineStr">
@@ -42268,7 +43153,7 @@
       </c>
       <c r="AP224" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ224" t="inlineStr">
@@ -42276,17 +43161,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR224" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS224" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1220</t>
         </is>
       </c>
       <c r="AT224" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU224" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV224" t="inlineStr">
@@ -42427,7 +43317,7 @@
       </c>
       <c r="AP225" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ225" t="inlineStr">
@@ -42435,17 +43325,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR225" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS225" t="inlineStr">
         <is>
           <t>SER_NO_FHI_303_MONTHLY</t>
         </is>
       </c>
       <c r="AT225" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU225" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV225" t="inlineStr">
@@ -42661,7 +43556,7 @@
       </c>
       <c r="AP226" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ226" t="inlineStr">
@@ -42669,17 +43564,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR226" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS226" t="inlineStr">
         <is>
           <t>SER_NO_FHI_303_MONTHLY</t>
         </is>
       </c>
       <c r="AT226" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU226" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV226" t="inlineStr">
@@ -42968,7 +43868,7 @@
       </c>
       <c r="AP228" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ228" t="inlineStr">
@@ -42976,17 +43876,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR228" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS228" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1220</t>
         </is>
       </c>
       <c r="AT228" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU228" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV228" t="inlineStr">
@@ -43202,7 +44107,7 @@
       </c>
       <c r="AP229" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ229" t="inlineStr">
@@ -43210,17 +44115,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR229" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS229" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1220</t>
         </is>
       </c>
       <c r="AT229" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU229" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV229" t="inlineStr">
@@ -43361,7 +44271,7 @@
       </c>
       <c r="AP230" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ230" t="inlineStr">
@@ -43369,17 +44279,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR230" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS230" t="inlineStr">
         <is>
           <t>SER_NO_FHI_303_MONTHLY</t>
         </is>
       </c>
       <c r="AT230" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU230" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV230" t="inlineStr">
@@ -43595,7 +44510,7 @@
       </c>
       <c r="AP231" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ231" t="inlineStr">
@@ -43603,17 +44518,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR231" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS231" t="inlineStr">
         <is>
           <t>SER_NO_FHI_303_MONTHLY</t>
         </is>
       </c>
       <c r="AT231" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU231" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV231" t="inlineStr">
@@ -43902,7 +44822,7 @@
       </c>
       <c r="AP233" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ233" t="inlineStr">
@@ -43910,17 +44830,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR233" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS233" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1220</t>
         </is>
       </c>
       <c r="AT233" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU233" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV233" t="inlineStr">
@@ -44136,7 +45061,7 @@
       </c>
       <c r="AP234" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ234" t="inlineStr">
@@ -44144,17 +45069,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR234" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS234" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1220</t>
         </is>
       </c>
       <c r="AT234" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU234" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV234" t="inlineStr">
@@ -44295,7 +45225,7 @@
       </c>
       <c r="AP235" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ235" t="inlineStr">
@@ -44303,17 +45233,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR235" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS235" t="inlineStr">
         <is>
           <t>SER_NO_FHI_303_MONTHLY</t>
         </is>
       </c>
       <c r="AT235" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU235" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV235" t="inlineStr">
@@ -44529,7 +45464,7 @@
       </c>
       <c r="AP236" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ236" t="inlineStr">
@@ -44537,17 +45472,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR236" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS236" t="inlineStr">
         <is>
           <t>SER_NO_FHI_303_MONTHLY</t>
         </is>
       </c>
       <c r="AT236" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU236" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV236" t="inlineStr">
@@ -44836,7 +45776,7 @@
       </c>
       <c r="AP238" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ238" t="inlineStr">
@@ -44844,17 +45784,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR238" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS238" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1220</t>
         </is>
       </c>
       <c r="AT238" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU238" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV238" t="inlineStr">
@@ -45070,7 +46015,7 @@
       </c>
       <c r="AP239" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ239" t="inlineStr">
@@ -45078,17 +46023,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR239" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS239" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1220</t>
         </is>
       </c>
       <c r="AT239" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU239" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV239" t="inlineStr">
@@ -45229,7 +46179,7 @@
       </c>
       <c r="AP240" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ240" t="inlineStr">
@@ -45237,17 +46187,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR240" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS240" t="inlineStr">
         <is>
           <t>SER_NO_FHI_303_MONTHLY</t>
         </is>
       </c>
       <c r="AT240" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU240" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV240" t="inlineStr">
@@ -45463,7 +46418,7 @@
       </c>
       <c r="AP241" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ241" t="inlineStr">
@@ -45471,17 +46426,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR241" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS241" t="inlineStr">
         <is>
           <t>SER_NO_FHI_303_MONTHLY</t>
         </is>
       </c>
       <c r="AT241" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU241" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV241" t="inlineStr">
@@ -45770,7 +46730,7 @@
       </c>
       <c r="AP243" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ243" t="inlineStr">
@@ -45778,17 +46738,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR243" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS243" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1220</t>
         </is>
       </c>
       <c r="AT243" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU243" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV243" t="inlineStr">
@@ -46004,7 +46969,7 @@
       </c>
       <c r="AP244" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ244" t="inlineStr">
@@ -46012,17 +46977,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR244" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS244" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1220</t>
         </is>
       </c>
       <c r="AT244" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU244" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV244" t="inlineStr">
@@ -46163,7 +47133,7 @@
       </c>
       <c r="AP245" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ245" t="inlineStr">
@@ -46171,17 +47141,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR245" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS245" t="inlineStr">
         <is>
           <t>SER_NO_FHI_303_MONTHLY</t>
         </is>
       </c>
       <c r="AT245" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU245" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV245" t="inlineStr">
@@ -46397,7 +47372,7 @@
       </c>
       <c r="AP246" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ246" t="inlineStr">
@@ -46405,17 +47380,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR246" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS246" t="inlineStr">
         <is>
           <t>SER_NO_FHI_303_MONTHLY</t>
         </is>
       </c>
       <c r="AT246" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU246" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV246" t="inlineStr">
@@ -46704,7 +47684,7 @@
       </c>
       <c r="AP248" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ248" t="inlineStr">
@@ -46712,17 +47692,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR248" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS248" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1220</t>
         </is>
       </c>
       <c r="AT248" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU248" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV248" t="inlineStr">
@@ -46938,7 +47923,7 @@
       </c>
       <c r="AP249" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ249" t="inlineStr">
@@ -46946,17 +47931,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR249" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS249" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1220</t>
         </is>
       </c>
       <c r="AT249" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU249" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV249" t="inlineStr">
@@ -47097,7 +48087,7 @@
       </c>
       <c r="AP250" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ250" t="inlineStr">
@@ -47105,17 +48095,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR250" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS250" t="inlineStr">
         <is>
           <t>SER_NO_FHI_303_MONTHLY</t>
         </is>
       </c>
       <c r="AT250" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU250" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV250" t="inlineStr">
@@ -47331,7 +48326,7 @@
       </c>
       <c r="AP251" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ251" t="inlineStr">
@@ -47339,17 +48334,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR251" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS251" t="inlineStr">
         <is>
           <t>SER_NO_FHI_303_MONTHLY</t>
         </is>
       </c>
       <c r="AT251" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU251" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV251" t="inlineStr">
@@ -47638,7 +48638,7 @@
       </c>
       <c r="AP253" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ253" t="inlineStr">
@@ -47646,17 +48646,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR253" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS253" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1220</t>
         </is>
       </c>
       <c r="AT253" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU253" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV253" t="inlineStr">
@@ -47872,7 +48877,7 @@
       </c>
       <c r="AP254" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ254" t="inlineStr">
@@ -47880,17 +48885,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR254" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS254" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1220</t>
         </is>
       </c>
       <c r="AT254" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU254" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV254" t="inlineStr">
@@ -48031,7 +49041,7 @@
       </c>
       <c r="AP255" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ255" t="inlineStr">
@@ -48039,17 +49049,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR255" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS255" t="inlineStr">
         <is>
           <t>SER_NO_FHI_303_MONTHLY</t>
         </is>
       </c>
       <c r="AT255" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU255" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV255" t="inlineStr">
@@ -48265,7 +49280,7 @@
       </c>
       <c r="AP256" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ256" t="inlineStr">
@@ -48273,17 +49288,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR256" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS256" t="inlineStr">
         <is>
           <t>SER_NO_FHI_303_MONTHLY</t>
         </is>
       </c>
       <c r="AT256" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU256" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV256" t="inlineStr">
@@ -48572,7 +49592,7 @@
       </c>
       <c r="AP258" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ258" t="inlineStr">
@@ -48580,17 +49600,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR258" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS258" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1220</t>
         </is>
       </c>
       <c r="AT258" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU258" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV258" t="inlineStr">
@@ -48806,7 +49831,7 @@
       </c>
       <c r="AP259" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ259" t="inlineStr">
@@ -48814,17 +49839,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR259" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS259" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1220</t>
         </is>
       </c>
       <c r="AT259" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU259" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV259" t="inlineStr">
@@ -48965,7 +49995,7 @@
       </c>
       <c r="AP260" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ260" t="inlineStr">
@@ -48973,17 +50003,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR260" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS260" t="inlineStr">
         <is>
           <t>SER_NO_FHI_303_MONTHLY</t>
         </is>
       </c>
       <c r="AT260" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU260" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV260" t="inlineStr">
@@ -49199,7 +50234,7 @@
       </c>
       <c r="AP261" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ261" t="inlineStr">
@@ -49207,17 +50242,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR261" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS261" t="inlineStr">
         <is>
           <t>SER_NO_FHI_303_MONTHLY</t>
         </is>
       </c>
       <c r="AT261" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU261" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV261" t="inlineStr">
@@ -49506,7 +50546,7 @@
       </c>
       <c r="AP263" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ263" t="inlineStr">
@@ -49514,17 +50554,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR263" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS263" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1220</t>
         </is>
       </c>
       <c r="AT263" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU263" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV263" t="inlineStr">
@@ -49740,7 +50785,7 @@
       </c>
       <c r="AP264" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ264" t="inlineStr">
@@ -49748,17 +50793,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR264" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS264" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1220</t>
         </is>
       </c>
       <c r="AT264" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU264" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV264" t="inlineStr">
@@ -49899,7 +50949,7 @@
       </c>
       <c r="AP265" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ265" t="inlineStr">
@@ -49907,17 +50957,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR265" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS265" t="inlineStr">
         <is>
           <t>SER_NO_FHI_303_MONTHLY</t>
         </is>
       </c>
       <c r="AT265" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU265" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV265" t="inlineStr">
@@ -50133,7 +51188,7 @@
       </c>
       <c r="AP266" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ266" t="inlineStr">
@@ -50141,17 +51196,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR266" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS266" t="inlineStr">
         <is>
           <t>SER_NO_FHI_303_MONTHLY</t>
         </is>
       </c>
       <c r="AT266" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU266" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV266" t="inlineStr">
@@ -50440,7 +51500,7 @@
       </c>
       <c r="AP268" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ268" t="inlineStr">
@@ -50448,17 +51508,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR268" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS268" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1220</t>
         </is>
       </c>
       <c r="AT268" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU268" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV268" t="inlineStr">
@@ -50674,7 +51739,7 @@
       </c>
       <c r="AP269" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ269" t="inlineStr">
@@ -50682,17 +51747,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR269" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS269" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1220</t>
         </is>
       </c>
       <c r="AT269" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU269" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV269" t="inlineStr">
@@ -50833,7 +51903,7 @@
       </c>
       <c r="AP270" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ270" t="inlineStr">
@@ -50841,17 +51911,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR270" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS270" t="inlineStr">
         <is>
           <t>SER_NO_FHI_303_MONTHLY</t>
         </is>
       </c>
       <c r="AT270" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU270" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV270" t="inlineStr">
@@ -51067,7 +52142,7 @@
       </c>
       <c r="AP271" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ271" t="inlineStr">
@@ -51075,17 +52150,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR271" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS271" t="inlineStr">
         <is>
           <t>SER_NO_FHI_303_MONTHLY</t>
         </is>
       </c>
       <c r="AT271" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU271" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV271" t="inlineStr">
@@ -51374,7 +52454,7 @@
       </c>
       <c r="AP273" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ273" t="inlineStr">
@@ -51382,17 +52462,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR273" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS273" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1220</t>
         </is>
       </c>
       <c r="AT273" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU273" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV273" t="inlineStr">
@@ -51608,7 +52693,7 @@
       </c>
       <c r="AP274" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ274" t="inlineStr">
@@ -51616,17 +52701,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR274" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS274" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1220</t>
         </is>
       </c>
       <c r="AT274" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU274" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV274" t="inlineStr">
@@ -51767,7 +52857,7 @@
       </c>
       <c r="AP275" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ275" t="inlineStr">
@@ -51775,17 +52865,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR275" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS275" t="inlineStr">
         <is>
           <t>SER_NO_FHI_303_MONTHLY</t>
         </is>
       </c>
       <c r="AT275" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU275" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV275" t="inlineStr">
@@ -52001,7 +53096,7 @@
       </c>
       <c r="AP276" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ276" t="inlineStr">
@@ -52009,17 +53104,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR276" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS276" t="inlineStr">
         <is>
           <t>SER_NO_FHI_303_MONTHLY</t>
         </is>
       </c>
       <c r="AT276" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU276" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV276" t="inlineStr">
@@ -52308,7 +53408,7 @@
       </c>
       <c r="AP278" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ278" t="inlineStr">
@@ -52316,17 +53416,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR278" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS278" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1220</t>
         </is>
       </c>
       <c r="AT278" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU278" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV278" t="inlineStr">
@@ -52542,7 +53647,7 @@
       </c>
       <c r="AP279" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ279" t="inlineStr">
@@ -52550,17 +53655,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR279" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS279" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1220</t>
         </is>
       </c>
       <c r="AT279" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU279" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV279" t="inlineStr">
@@ -52701,7 +53811,7 @@
       </c>
       <c r="AP280" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ280" t="inlineStr">
@@ -52709,17 +53819,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR280" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS280" t="inlineStr">
         <is>
           <t>SER_NO_FHI_303_MONTHLY</t>
         </is>
       </c>
       <c r="AT280" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU280" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV280" t="inlineStr">
@@ -52935,7 +54050,7 @@
       </c>
       <c r="AP281" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ281" t="inlineStr">
@@ -52943,17 +54058,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR281" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS281" t="inlineStr">
         <is>
           <t>SER_NO_FHI_303_MONTHLY</t>
         </is>
       </c>
       <c r="AT281" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU281" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV281" t="inlineStr">
@@ -53242,7 +54362,7 @@
       </c>
       <c r="AP283" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ283" t="inlineStr">
@@ -53250,17 +54370,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR283" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS283" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1220</t>
         </is>
       </c>
       <c r="AT283" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU283" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV283" t="inlineStr">
@@ -53476,7 +54601,7 @@
       </c>
       <c r="AP284" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ284" t="inlineStr">
@@ -53484,17 +54609,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR284" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS284" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1220</t>
         </is>
       </c>
       <c r="AT284" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU284" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV284" t="inlineStr">
@@ -53635,7 +54765,7 @@
       </c>
       <c r="AP285" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ285" t="inlineStr">
@@ -53643,17 +54773,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR285" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS285" t="inlineStr">
         <is>
           <t>SER_NO_FHI_303_MONTHLY</t>
         </is>
       </c>
       <c r="AT285" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU285" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV285" t="inlineStr">
@@ -53869,7 +55004,7 @@
       </c>
       <c r="AP286" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ286" t="inlineStr">
@@ -53877,17 +55012,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR286" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS286" t="inlineStr">
         <is>
           <t>SER_NO_FHI_303_MONTHLY</t>
         </is>
       </c>
       <c r="AT286" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU286" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV286" t="inlineStr">
@@ -54176,7 +55316,7 @@
       </c>
       <c r="AP288" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ288" t="inlineStr">
@@ -54184,17 +55324,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR288" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS288" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1220</t>
         </is>
       </c>
       <c r="AT288" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU288" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV288" t="inlineStr">
@@ -54410,7 +55555,7 @@
       </c>
       <c r="AP289" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ289" t="inlineStr">
@@ -54418,17 +55563,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR289" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS289" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1220</t>
         </is>
       </c>
       <c r="AT289" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU289" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV289" t="inlineStr">
@@ -54569,7 +55719,7 @@
       </c>
       <c r="AP290" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ290" t="inlineStr">
@@ -54577,17 +55727,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR290" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS290" t="inlineStr">
         <is>
           <t>SER_NO_FHI_303_MONTHLY</t>
         </is>
       </c>
       <c r="AT290" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU290" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV290" t="inlineStr">
@@ -54803,7 +55958,7 @@
       </c>
       <c r="AP291" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ291" t="inlineStr">
@@ -54811,17 +55966,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR291" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS291" t="inlineStr">
         <is>
           <t>SER_NO_FHI_303_MONTHLY</t>
         </is>
       </c>
       <c r="AT291" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU291" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV291" t="inlineStr">
@@ -55110,7 +56270,7 @@
       </c>
       <c r="AP293" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ293" t="inlineStr">
@@ -55118,17 +56278,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR293" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS293" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1220</t>
         </is>
       </c>
       <c r="AT293" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU293" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV293" t="inlineStr">
@@ -55344,7 +56509,7 @@
       </c>
       <c r="AP294" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ294" t="inlineStr">
@@ -55352,17 +56517,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR294" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS294" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1220</t>
         </is>
       </c>
       <c r="AT294" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU294" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV294" t="inlineStr">
@@ -55503,7 +56673,7 @@
       </c>
       <c r="AP295" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ295" t="inlineStr">
@@ -55511,17 +56681,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR295" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS295" t="inlineStr">
         <is>
           <t>SER_NO_FHI_303_MONTHLY</t>
         </is>
       </c>
       <c r="AT295" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU295" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV295" t="inlineStr">
@@ -55737,7 +56912,7 @@
       </c>
       <c r="AP296" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ296" t="inlineStr">
@@ -55745,17 +56920,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR296" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS296" t="inlineStr">
         <is>
           <t>SER_NO_FHI_303_MONTHLY</t>
         </is>
       </c>
       <c r="AT296" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU296" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV296" t="inlineStr">
@@ -56044,7 +57224,7 @@
       </c>
       <c r="AP298" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ298" t="inlineStr">
@@ -56052,17 +57232,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR298" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS298" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1220</t>
         </is>
       </c>
       <c r="AT298" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU298" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV298" t="inlineStr">
@@ -56278,7 +57463,7 @@
       </c>
       <c r="AP299" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ299" t="inlineStr">
@@ -56286,17 +57471,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR299" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS299" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1220</t>
         </is>
       </c>
       <c r="AT299" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU299" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV299" t="inlineStr">
@@ -56437,7 +57627,7 @@
       </c>
       <c r="AP300" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ300" t="inlineStr">
@@ -56445,17 +57635,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR300" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS300" t="inlineStr">
         <is>
           <t>SER_NO_FHI_303_MONTHLY</t>
         </is>
       </c>
       <c r="AT300" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU300" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV300" t="inlineStr">
@@ -56671,7 +57866,7 @@
       </c>
       <c r="AP301" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ301" t="inlineStr">
@@ -56679,17 +57874,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR301" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS301" t="inlineStr">
         <is>
           <t>SER_NO_FHI_303_MONTHLY</t>
         </is>
       </c>
       <c r="AT301" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU301" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV301" t="inlineStr">
